--- a/data/macro/Retail Sales.xlsx
+++ b/data/macro/Retail Sales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/macro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E2575C-4531-4516-BEA1-D229FE683C00}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16700DA-F494-3E43-A9B9-F998AC2F3A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="1" xr2:uid="{30656A32-0D37-469D-885D-F50C8A2BA9DC}"/>
+    <workbookView xWindow="18000" yWindow="780" windowWidth="18000" windowHeight="20760" xr2:uid="{30656A32-0D37-469D-885D-F50C8A2BA9DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Retail Sales" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Release Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,16 +59,20 @@
     <t>https://fred.stlouisfed.org/series/RSAFS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Time</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="170" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -112,6 +116,12 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -134,7 +144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -144,11 +154,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -157,13 +167,13 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3">
@@ -172,12 +182,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="백분율" xfId="2" builtinId="5"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="3" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -193,9 +209,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -233,7 +249,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -339,7 +355,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -481,7 +497,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -489,4547 +505,6057 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A423BD41-4AF5-471C-B1B1-976B1BB48C33}">
-  <dimension ref="A1:F407"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G407"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="5"/>
-    <col min="6" max="6" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" style="5"/>
+    <col min="7" max="7" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>33604</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D2" s="6">
         <v>159177</v>
       </c>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>33635</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D3" s="6">
         <v>159189</v>
       </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>33664</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D4" s="6">
         <v>158647</v>
       </c>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>33695</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D5" s="6">
         <v>159921</v>
       </c>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>33725</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D6" s="6">
         <v>160471</v>
       </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>33756</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D7" s="6">
         <v>161205</v>
       </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>33786</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D8" s="6">
         <v>162855</v>
       </c>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>33817</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D9" s="6">
         <v>162412</v>
       </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>33848</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D10" s="6">
         <v>164361</v>
       </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>33878</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D11" s="6">
         <v>166063</v>
       </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>33909</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D12" s="6">
         <v>166124</v>
       </c>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>33939</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D13" s="6">
         <v>167691</v>
       </c>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>33970</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D14" s="6">
         <v>169500</v>
       </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>34001</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D15" s="6">
         <v>168840</v>
       </c>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>34029</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D16" s="6">
         <v>167682</v>
       </c>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>34060</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D17" s="6">
         <v>172102</v>
       </c>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>34090</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D18" s="6">
         <v>172960</v>
       </c>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>34121</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D19" s="6">
         <v>173018</v>
       </c>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>34151</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D20" s="6">
         <v>175822</v>
       </c>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>34182</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D21" s="6">
         <v>175233</v>
       </c>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>34213</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D22" s="6">
         <v>176608</v>
       </c>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>34243</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D23" s="6">
         <v>177588</v>
       </c>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>34274</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D24" s="6">
         <v>179758</v>
       </c>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>34304</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D25" s="6">
         <v>181077</v>
       </c>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>34335</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D26" s="6">
         <v>179615</v>
       </c>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>34366</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D27" s="6">
         <v>183101</v>
       </c>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>34394</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D28" s="6">
         <v>186721</v>
       </c>
-      <c r="F28" s="3"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>34425</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D29" s="6">
         <v>186423</v>
       </c>
-      <c r="F29" s="3"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>34455</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D30" s="6">
         <v>185616</v>
       </c>
-      <c r="F30" s="3"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>34486</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D31" s="6">
         <v>187800</v>
       </c>
-      <c r="F31" s="3"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1">
         <v>34516</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D32" s="6">
         <v>188062</v>
       </c>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1">
         <v>34547</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D33" s="6">
         <v>190771</v>
       </c>
-      <c r="F33" s="3"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1">
         <v>34578</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D34" s="6">
         <v>192585</v>
       </c>
-      <c r="F34" s="3"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1">
         <v>34608</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D35" s="6">
         <v>193914</v>
       </c>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1">
         <v>34639</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D36" s="6">
         <v>194425</v>
       </c>
-      <c r="F36" s="3"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1">
         <v>34669</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D37" s="6">
         <v>194939</v>
       </c>
-      <c r="F37" s="3"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1">
         <v>34700</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D38" s="6">
         <v>195908</v>
       </c>
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1">
         <v>34731</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D39" s="6">
         <v>193068</v>
       </c>
-      <c r="F39" s="3"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39" s="3"/>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="1">
         <v>34759</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D40" s="6">
         <v>195179</v>
       </c>
-      <c r="F40" s="3"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40" s="3"/>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1">
         <v>34790</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D41" s="6">
         <v>195310</v>
       </c>
-      <c r="F41" s="3"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1">
         <v>34820</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D42" s="6">
         <v>198060</v>
       </c>
-      <c r="F42" s="3"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42" s="3"/>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="1">
         <v>34851</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D43" s="6">
         <v>200383</v>
       </c>
-      <c r="F43" s="3"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G43" s="3"/>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="1">
         <v>34881</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D44" s="6">
         <v>199110</v>
       </c>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G44" s="3"/>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1">
         <v>34912</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D45" s="6">
         <v>201078</v>
       </c>
-      <c r="F45" s="3"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G45" s="3"/>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1">
         <v>34943</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D46" s="6">
         <v>201337</v>
       </c>
-      <c r="F46" s="3"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G46" s="3"/>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="1">
         <v>34973</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D47" s="6">
         <v>200597</v>
       </c>
-      <c r="F47" s="3"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G47" s="3"/>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="1">
         <v>35004</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D48" s="6">
         <v>203545</v>
       </c>
-      <c r="F48" s="3"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G48" s="3"/>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="1">
         <v>35034</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D49" s="6">
         <v>204032</v>
       </c>
-      <c r="F49" s="3"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G49" s="3"/>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="1">
         <v>35065</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D50" s="6">
         <v>203793</v>
       </c>
-      <c r="F50" s="3"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G50" s="3"/>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="1">
         <v>35096</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D51" s="6">
         <v>206875</v>
       </c>
-      <c r="F51" s="3"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G51" s="3"/>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="1">
         <v>35125</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D52" s="6">
         <v>207650</v>
       </c>
-      <c r="F52" s="3"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G52" s="3"/>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="1">
         <v>35156</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D53" s="6">
         <v>209294</v>
       </c>
-      <c r="F53" s="3"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G53" s="3"/>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="1">
         <v>35186</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D54" s="6">
         <v>211157</v>
       </c>
-      <c r="F54" s="3"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G54" s="3"/>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="1">
         <v>35217</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D55" s="6">
         <v>209474</v>
       </c>
-      <c r="F55" s="3"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G55" s="3"/>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="1">
         <v>35247</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D56" s="6">
         <v>210827</v>
       </c>
-      <c r="F56" s="3"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G56" s="3"/>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="1">
         <v>35278</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D57" s="6">
         <v>210846</v>
       </c>
-      <c r="F57" s="3"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G57" s="3"/>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="1">
         <v>35309</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D58" s="6">
         <v>213233</v>
       </c>
-      <c r="F58" s="3"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G58" s="3"/>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" s="1">
         <v>35339</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D59" s="6">
         <v>215526</v>
       </c>
-      <c r="F59" s="3"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G59" s="3"/>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" s="1">
         <v>35370</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D60" s="6">
         <v>215167</v>
       </c>
-      <c r="F60" s="3"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G60" s="3"/>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" s="1">
         <v>35400</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D61" s="6">
         <v>215690</v>
       </c>
-      <c r="F61" s="3"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G61" s="3"/>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" s="1">
         <v>35431</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D62" s="6">
         <v>218124</v>
       </c>
-      <c r="F62" s="3"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G62" s="3"/>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" s="1">
         <v>35462</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D63" s="6">
         <v>219587</v>
       </c>
-      <c r="F63" s="3"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G63" s="3"/>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" s="1">
         <v>35490</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D64" s="6">
         <v>221189</v>
       </c>
-      <c r="F64" s="3"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G64" s="3"/>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" s="1">
         <v>35521</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D65" s="6">
         <v>217925</v>
       </c>
-      <c r="F65" s="3"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G65" s="3"/>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" s="1">
         <v>35551</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D66" s="6">
         <v>217771</v>
       </c>
-      <c r="F66" s="3"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G66" s="3"/>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" s="1">
         <v>35582</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D67" s="6">
         <v>220233</v>
       </c>
-      <c r="F67" s="3"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G67" s="3"/>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" s="1">
         <v>35612</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D68" s="6">
         <v>222985</v>
       </c>
-      <c r="F68" s="3"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G68" s="3"/>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" s="1">
         <v>35643</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D69" s="6">
         <v>223120</v>
       </c>
-      <c r="F69" s="3"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G69" s="3"/>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" s="1">
         <v>35674</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D70" s="6">
         <v>224509</v>
       </c>
-      <c r="F70" s="3"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G70" s="3"/>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" s="1">
         <v>35704</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D71" s="6">
         <v>224300</v>
       </c>
-      <c r="F71" s="3"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G71" s="3"/>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" s="1">
         <v>35735</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D72" s="6">
         <v>223718</v>
       </c>
-      <c r="F72" s="3"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G72" s="3"/>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" s="1">
         <v>35765</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D73" s="6">
         <v>225236</v>
       </c>
-      <c r="F73" s="3"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G73" s="3"/>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" s="1">
         <v>35796</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D74" s="6">
         <v>225954</v>
       </c>
-      <c r="F74" s="3"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G74" s="3"/>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" s="1">
         <v>35827</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D75" s="6">
         <v>225746</v>
       </c>
-      <c r="F75" s="3"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G75" s="3"/>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" s="1">
         <v>35855</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D76" s="6">
         <v>226889</v>
       </c>
-      <c r="F76" s="3"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G76" s="3"/>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" s="1">
         <v>35886</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D77" s="6">
         <v>230409</v>
       </c>
-      <c r="F77" s="3"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G77" s="3"/>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" s="1">
         <v>35916</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D78" s="6">
         <v>230995</v>
       </c>
-      <c r="F78" s="3"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G78" s="3"/>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" s="1">
         <v>35947</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D79" s="6">
         <v>233207</v>
       </c>
-      <c r="F79" s="3"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G79" s="3"/>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" s="1">
         <v>35977</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D80" s="6">
         <v>231551</v>
       </c>
-      <c r="F80" s="3"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G80" s="3"/>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" s="1">
         <v>36008</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D81" s="6">
         <v>229792</v>
       </c>
-      <c r="F81" s="3"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G81" s="3"/>
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82" s="1">
         <v>36039</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D82" s="6">
         <v>232308</v>
       </c>
-      <c r="F82" s="3"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G82" s="3"/>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" s="1">
         <v>36069</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D83" s="6">
         <v>236174</v>
       </c>
-      <c r="F83" s="3"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G83" s="3"/>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" s="1">
         <v>36100</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C84" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D84" s="6">
         <v>237592</v>
       </c>
-      <c r="F84" s="3"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G84" s="3"/>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85" s="1">
         <v>36130</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D85" s="6">
         <v>240140</v>
       </c>
-      <c r="F85" s="3"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G85" s="3"/>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" s="1">
         <v>36161</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D86" s="6">
         <v>240269</v>
       </c>
-      <c r="F86" s="3"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G86" s="3"/>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" s="1">
         <v>36192</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D87" s="6">
         <v>243346</v>
       </c>
-      <c r="F87" s="3"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G87" s="3"/>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" s="1">
         <v>36220</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D88" s="6">
         <v>244687</v>
       </c>
-      <c r="F88" s="3"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G88" s="3"/>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" s="1">
         <v>36251</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C89" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D89" s="6">
         <v>246628</v>
       </c>
-      <c r="F89" s="3"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G89" s="3"/>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90" s="1">
         <v>36281</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D90" s="6">
         <v>248367</v>
       </c>
-      <c r="F90" s="3"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G90" s="3"/>
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91" s="1">
         <v>36312</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D91" s="6">
         <v>249329</v>
       </c>
-      <c r="F91" s="3"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G91" s="3"/>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92" s="1">
         <v>36342</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D92" s="6">
         <v>251263</v>
       </c>
-      <c r="F92" s="3"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G92" s="3"/>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93" s="1">
         <v>36373</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D93" s="6">
         <v>253844</v>
       </c>
-      <c r="F93" s="3"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G93" s="3"/>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" s="1">
         <v>36404</v>
       </c>
-      <c r="C94" s="6">
+      <c r="C94" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D94" s="6">
         <v>255029</v>
       </c>
-      <c r="F94" s="3"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G94" s="3"/>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" s="1">
         <v>36434</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C95" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D95" s="6">
         <v>254816</v>
       </c>
-      <c r="F95" s="3"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G95" s="3"/>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96" s="1">
         <v>36465</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D96" s="6">
         <v>258133</v>
       </c>
-      <c r="F96" s="3"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G96" s="3"/>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97" s="1">
         <v>36495</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C97" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D97" s="6">
         <v>263311</v>
       </c>
-      <c r="F97" s="3"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G97" s="3"/>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98" s="1">
         <v>36526</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C98" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D98" s="6">
         <v>261545</v>
       </c>
-      <c r="F98" s="3"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G98" s="3"/>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99" s="1">
         <v>36557</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C99" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D99" s="6">
         <v>265686</v>
       </c>
-      <c r="F99" s="3"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G99" s="3"/>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100" s="1">
         <v>36586</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D100" s="6">
         <v>269019</v>
       </c>
-      <c r="F100" s="3"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G100" s="3"/>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101" s="1">
         <v>36617</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C101" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D101" s="6">
         <v>264067</v>
       </c>
-      <c r="F101" s="3"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G101" s="3"/>
+    </row>
+    <row r="102" spans="1:7">
       <c r="A102" s="1">
         <v>36647</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D102" s="6">
         <v>265992</v>
       </c>
-      <c r="F102" s="3"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G102" s="3"/>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103" s="1">
         <v>36678</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C103" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D103" s="6">
         <v>267750</v>
       </c>
-      <c r="F103" s="3"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G103" s="3"/>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104" s="1">
         <v>36708</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C104" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D104" s="6">
         <v>265683</v>
       </c>
-      <c r="F104" s="3"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G104" s="3"/>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105" s="1">
         <v>36739</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C105" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D105" s="6">
         <v>266885</v>
       </c>
-      <c r="F105" s="3"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G105" s="3"/>
+    </row>
+    <row r="106" spans="1:7">
       <c r="A106" s="1">
         <v>36770</v>
       </c>
-      <c r="C106" s="6">
+      <c r="C106" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D106" s="6">
         <v>270523</v>
       </c>
-      <c r="F106" s="3"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G106" s="3"/>
+    </row>
+    <row r="107" spans="1:7">
       <c r="A107" s="1">
         <v>36800</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D107" s="6">
         <v>270339</v>
       </c>
-      <c r="F107" s="3"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G107" s="3"/>
+    </row>
+    <row r="108" spans="1:7">
       <c r="A108" s="1">
         <v>36831</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D108" s="6">
         <v>268850</v>
       </c>
-      <c r="F108" s="3"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G108" s="3"/>
+    </row>
+    <row r="109" spans="1:7">
       <c r="A109" s="1">
         <v>36861</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C109" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D109" s="6">
         <v>268338</v>
       </c>
-      <c r="F109" s="3"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G109" s="3"/>
+    </row>
+    <row r="110" spans="1:7">
       <c r="A110" s="1">
         <v>36892</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C110" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D110" s="6">
         <v>272881</v>
       </c>
-      <c r="F110" s="3"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G110" s="3"/>
+    </row>
+    <row r="111" spans="1:7">
       <c r="A111" s="1">
         <v>36923</v>
       </c>
-      <c r="C111" s="6">
+      <c r="C111" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D111" s="6">
         <v>272627</v>
       </c>
-      <c r="F111" s="3"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G111" s="3"/>
+    </row>
+    <row r="112" spans="1:7">
       <c r="A112" s="1">
         <v>36951</v>
       </c>
-      <c r="C112" s="6">
+      <c r="C112" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D112" s="6">
         <v>269820</v>
       </c>
-      <c r="F112" s="3"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G112" s="3"/>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" s="1">
         <v>36982</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C113" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D113" s="6">
         <v>274410</v>
       </c>
-      <c r="F113" s="3"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G113" s="3"/>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" s="1">
         <v>37012</v>
       </c>
       <c r="B114" s="4">
         <v>37055</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C114" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D114" s="6">
         <v>275769</v>
       </c>
-      <c r="F114" s="3"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G114" s="3"/>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" s="1">
         <v>37043</v>
       </c>
       <c r="B115" s="4">
         <v>37085</v>
       </c>
-      <c r="C115" s="6">
+      <c r="C115" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D115" s="6">
         <v>274474</v>
       </c>
-      <c r="F115" s="3"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G115" s="3"/>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" s="1">
         <v>37073</v>
       </c>
       <c r="B116" s="4">
         <v>37117</v>
       </c>
-      <c r="C116" s="6">
+      <c r="C116" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D116" s="6">
         <v>273098</v>
       </c>
-      <c r="F116" s="3"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G116" s="3"/>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" s="1">
         <v>37104</v>
       </c>
       <c r="B117" s="4">
         <v>37148</v>
       </c>
-      <c r="C117" s="6">
+      <c r="C117" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D117" s="6">
         <v>275659</v>
       </c>
-      <c r="F117" s="3"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G117" s="3"/>
+    </row>
+    <row r="118" spans="1:7">
       <c r="A118" s="1">
         <v>37135</v>
       </c>
       <c r="B118" s="4">
         <v>37176</v>
       </c>
-      <c r="C118" s="6">
+      <c r="C118" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D118" s="6">
         <v>268652</v>
       </c>
-      <c r="F118" s="3"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G118" s="3"/>
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" s="1">
         <v>37165</v>
       </c>
       <c r="B119" s="4">
         <v>37209</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C119" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D119" s="6">
         <v>288632</v>
       </c>
-      <c r="F119" s="3"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G119" s="3"/>
+    </row>
+    <row r="120" spans="1:7">
       <c r="A120" s="1">
         <v>37196</v>
       </c>
       <c r="B120" s="4">
         <v>37238</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D120" s="6">
         <v>280033</v>
       </c>
-      <c r="F120" s="3"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G120" s="3"/>
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" s="1">
         <v>37226</v>
       </c>
       <c r="B121" s="4">
         <v>37271</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D121" s="6">
         <v>276302</v>
       </c>
-      <c r="F121" s="3"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G121" s="3"/>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" s="1">
         <v>37257</v>
       </c>
       <c r="B122" s="4">
         <v>37300</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D122" s="6">
         <v>277135</v>
       </c>
-      <c r="F122" s="3"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G122" s="3"/>
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" s="1">
         <v>37288</v>
       </c>
       <c r="B123" s="4">
         <v>37328</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C123" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D123" s="6">
         <v>278869</v>
       </c>
-      <c r="F123" s="3"/>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G123" s="3"/>
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" s="1">
         <v>37316</v>
       </c>
       <c r="B124" s="4">
         <v>37358</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D124" s="6">
         <v>278079</v>
       </c>
-      <c r="F124" s="3"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G124" s="3"/>
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" s="1">
         <v>37347</v>
       </c>
       <c r="B125" s="4">
         <v>37390</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D125" s="6">
         <v>281147</v>
       </c>
-      <c r="F125" s="3"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G125" s="3"/>
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" s="1">
         <v>37377</v>
       </c>
       <c r="B126" s="4">
         <v>37420</v>
       </c>
-      <c r="C126" s="6">
+      <c r="C126" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D126" s="6">
         <v>278966</v>
       </c>
-      <c r="F126" s="3"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G126" s="3"/>
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" s="1">
         <v>37408</v>
       </c>
       <c r="B127" s="4">
         <v>37449</v>
       </c>
-      <c r="C127" s="6">
+      <c r="C127" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D127" s="6">
         <v>280426</v>
       </c>
-      <c r="F127" s="3"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G127" s="3"/>
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" s="1">
         <v>37438</v>
       </c>
       <c r="B128" s="4">
         <v>37481</v>
       </c>
-      <c r="C128" s="6">
+      <c r="C128" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D128" s="6">
         <v>284161</v>
       </c>
-      <c r="F128" s="3"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G128" s="3"/>
+    </row>
+    <row r="129" spans="1:7">
       <c r="A129" s="1">
         <v>37469</v>
       </c>
       <c r="B129" s="4">
         <v>37512</v>
       </c>
-      <c r="C129" s="6">
+      <c r="C129" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D129" s="6">
         <v>285884</v>
       </c>
-      <c r="F129" s="3"/>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G129" s="3"/>
+    </row>
+    <row r="130" spans="1:7">
       <c r="A130" s="1">
         <v>37500</v>
       </c>
       <c r="B130" s="4">
         <v>37540</v>
       </c>
-      <c r="C130" s="6">
+      <c r="C130" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D130" s="6">
         <v>281064</v>
       </c>
-      <c r="F130" s="3"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G130" s="3"/>
+    </row>
+    <row r="131" spans="1:7">
       <c r="A131" s="1">
         <v>37530</v>
       </c>
       <c r="B131" s="4">
         <v>37574</v>
       </c>
-      <c r="C131" s="6">
+      <c r="C131" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D131" s="6">
         <v>282940</v>
       </c>
-      <c r="F131" s="3"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G131" s="3"/>
+    </row>
+    <row r="132" spans="1:7">
       <c r="A132" s="1">
         <v>37561</v>
       </c>
       <c r="B132" s="4">
         <v>37602</v>
       </c>
-      <c r="C132" s="6">
+      <c r="C132" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D132" s="6">
         <v>283408</v>
       </c>
-      <c r="F132" s="3"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G132" s="3"/>
+    </row>
+    <row r="133" spans="1:7">
       <c r="A133" s="1">
         <v>37591</v>
       </c>
       <c r="B133" s="4">
         <v>37635</v>
       </c>
-      <c r="C133" s="6">
+      <c r="C133" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D133" s="6">
         <v>286646</v>
       </c>
-      <c r="F133" s="3"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G133" s="3"/>
+    </row>
+    <row r="134" spans="1:7">
       <c r="A134" s="1">
         <v>37622</v>
       </c>
       <c r="B134" s="4">
         <v>37665</v>
       </c>
-      <c r="C134" s="6">
+      <c r="C134" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D134" s="6">
         <v>288657</v>
       </c>
-      <c r="F134" s="3"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G134" s="3"/>
+    </row>
+    <row r="135" spans="1:7">
       <c r="A135" s="1">
         <v>37653</v>
       </c>
       <c r="B135" s="4">
         <v>37693</v>
       </c>
-      <c r="C135" s="6">
+      <c r="C135" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D135" s="6">
         <v>284696</v>
       </c>
-      <c r="F135" s="3"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G135" s="3"/>
+    </row>
+    <row r="136" spans="1:7">
       <c r="A136" s="1">
         <v>37681</v>
       </c>
       <c r="B136" s="4">
         <v>37722</v>
       </c>
-      <c r="C136" s="6">
+      <c r="C136" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D136" s="6">
         <v>288177</v>
       </c>
-      <c r="F136" s="3"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G136" s="3"/>
+    </row>
+    <row r="137" spans="1:7">
       <c r="A137" s="1">
         <v>37712</v>
       </c>
       <c r="B137" s="4">
         <v>37755</v>
       </c>
-      <c r="C137" s="6">
+      <c r="C137" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D137" s="6">
         <v>289053</v>
       </c>
-      <c r="F137" s="3"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G137" s="3"/>
+    </row>
+    <row r="138" spans="1:7">
       <c r="A138" s="1">
         <v>37742</v>
       </c>
       <c r="B138" s="4">
         <v>37784</v>
       </c>
-      <c r="C138" s="6">
+      <c r="C138" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D138" s="6">
         <v>289619</v>
       </c>
-      <c r="F138" s="3"/>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G138" s="3"/>
+    </row>
+    <row r="139" spans="1:7">
       <c r="A139" s="1">
         <v>37773</v>
       </c>
       <c r="B139" s="4">
         <v>37817</v>
       </c>
-      <c r="C139" s="6">
+      <c r="C139" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D139" s="6">
         <v>293671</v>
       </c>
-      <c r="F139" s="3"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G139" s="3"/>
+    </row>
+    <row r="140" spans="1:7">
       <c r="A140" s="1">
         <v>37803</v>
       </c>
       <c r="B140" s="4">
         <v>37846</v>
       </c>
-      <c r="C140" s="6">
+      <c r="C140" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D140" s="6">
         <v>296207</v>
       </c>
-      <c r="F140" s="3"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G140" s="3"/>
+    </row>
+    <row r="141" spans="1:7">
       <c r="A141" s="1">
         <v>37834</v>
       </c>
       <c r="B141" s="4">
         <v>37876</v>
       </c>
-      <c r="C141" s="6">
+      <c r="C141" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D141" s="6">
         <v>299592</v>
       </c>
-      <c r="F141" s="3"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G141" s="3"/>
+    </row>
+    <row r="142" spans="1:7">
       <c r="A142" s="1">
         <v>37865</v>
       </c>
       <c r="B142" s="4">
         <v>37909</v>
       </c>
-      <c r="C142" s="6">
+      <c r="C142" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D142" s="6">
         <v>298921</v>
       </c>
-      <c r="F142" s="3"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G142" s="3"/>
+    </row>
+    <row r="143" spans="1:7">
       <c r="A143" s="1">
         <v>37895</v>
       </c>
       <c r="B143" s="4">
         <v>37939</v>
       </c>
-      <c r="C143" s="6">
+      <c r="C143" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D143" s="6">
         <v>298205</v>
       </c>
-      <c r="F143" s="3"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G143" s="3"/>
+    </row>
+    <row r="144" spans="1:7">
       <c r="A144" s="1">
         <v>37926</v>
       </c>
       <c r="B144" s="4">
         <v>37966</v>
       </c>
-      <c r="C144" s="6">
+      <c r="C144" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D144" s="6">
         <v>299433</v>
       </c>
-      <c r="F144" s="3"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G144" s="3"/>
+    </row>
+    <row r="145" spans="1:7">
       <c r="A145" s="1">
         <v>37956</v>
       </c>
       <c r="B145" s="4">
         <v>38001</v>
       </c>
-      <c r="C145" s="6">
+      <c r="C145" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D145" s="6">
         <v>300702</v>
       </c>
-      <c r="F145" s="3"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G145" s="3"/>
+    </row>
+    <row r="146" spans="1:7">
       <c r="A146" s="1">
         <v>37987</v>
       </c>
       <c r="B146" s="4">
         <v>38029</v>
       </c>
-      <c r="C146" s="6">
+      <c r="C146" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D146" s="6">
         <v>301993</v>
       </c>
-      <c r="F146" s="3"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G146" s="3"/>
+    </row>
+    <row r="147" spans="1:7">
       <c r="A147" s="1">
         <v>38018</v>
       </c>
       <c r="B147" s="4">
         <v>38057</v>
       </c>
-      <c r="C147" s="6">
+      <c r="C147" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D147" s="6">
         <v>303915</v>
       </c>
-      <c r="F147" s="3"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G147" s="3"/>
+    </row>
+    <row r="148" spans="1:7">
       <c r="A148" s="1">
         <v>38047</v>
       </c>
       <c r="B148" s="4">
         <v>38090</v>
       </c>
-      <c r="C148" s="6">
+      <c r="C148" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D148" s="6">
         <v>309471</v>
       </c>
-      <c r="F148" s="3"/>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G148" s="3"/>
+    </row>
+    <row r="149" spans="1:7">
       <c r="A149" s="1">
         <v>38078</v>
       </c>
       <c r="B149" s="4">
         <v>38120</v>
       </c>
-      <c r="C149" s="6">
+      <c r="C149" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D149" s="6">
         <v>307358</v>
       </c>
-      <c r="F149" s="3"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G149" s="3"/>
+    </row>
+    <row r="150" spans="1:7">
       <c r="A150" s="1">
         <v>38108</v>
       </c>
       <c r="B150" s="4">
         <v>38152</v>
       </c>
-      <c r="C150" s="6">
+      <c r="C150" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D150" s="6">
         <v>311088</v>
       </c>
-      <c r="F150" s="3"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G150" s="3"/>
+    </row>
+    <row r="151" spans="1:7">
       <c r="A151" s="1">
         <v>38139</v>
       </c>
       <c r="B151" s="4">
         <v>38182</v>
       </c>
-      <c r="C151" s="6">
+      <c r="C151" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D151" s="6">
         <v>309127</v>
       </c>
-      <c r="F151" s="3"/>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G151" s="3"/>
+    </row>
+    <row r="152" spans="1:7">
       <c r="A152" s="1">
         <v>38169</v>
       </c>
       <c r="B152" s="4">
         <v>38211</v>
       </c>
-      <c r="C152" s="6">
+      <c r="C152" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D152" s="6">
         <v>311681</v>
       </c>
-      <c r="F152" s="3"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G152" s="3"/>
+    </row>
+    <row r="153" spans="1:7">
       <c r="A153" s="1">
         <v>38200</v>
       </c>
       <c r="B153" s="4">
         <v>38244</v>
       </c>
-      <c r="C153" s="6">
+      <c r="C153" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D153" s="6">
         <v>311192</v>
       </c>
-      <c r="F153" s="3"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G153" s="3"/>
+    </row>
+    <row r="154" spans="1:7">
       <c r="A154" s="1">
         <v>38231</v>
       </c>
       <c r="B154" s="4">
         <v>38275</v>
       </c>
-      <c r="C154" s="6">
+      <c r="C154" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D154" s="6">
         <v>317446</v>
       </c>
-      <c r="F154" s="3"/>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G154" s="3"/>
+    </row>
+    <row r="155" spans="1:7">
       <c r="A155" s="1">
         <v>38261</v>
       </c>
       <c r="B155" s="4">
         <v>38303</v>
       </c>
-      <c r="C155" s="6">
+      <c r="C155" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D155" s="6">
         <v>318476</v>
       </c>
-      <c r="F155" s="3"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G155" s="3"/>
+    </row>
+    <row r="156" spans="1:7">
       <c r="A156" s="1">
         <v>38292</v>
       </c>
       <c r="B156" s="4">
         <v>38334</v>
       </c>
-      <c r="C156" s="6">
+      <c r="C156" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D156" s="6">
         <v>320520</v>
       </c>
-      <c r="F156" s="3"/>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G156" s="3"/>
+    </row>
+    <row r="157" spans="1:7">
       <c r="A157" s="1">
         <v>38322</v>
       </c>
       <c r="B157" s="4">
         <v>38365</v>
       </c>
-      <c r="C157" s="6">
+      <c r="C157" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D157" s="6">
         <v>324672</v>
       </c>
-      <c r="F157" s="3"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G157" s="3"/>
+    </row>
+    <row r="158" spans="1:7">
       <c r="A158" s="1">
         <v>38353</v>
       </c>
       <c r="B158" s="4">
         <v>38398</v>
       </c>
-      <c r="C158" s="6">
+      <c r="C158" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D158" s="6">
         <v>321272</v>
       </c>
-      <c r="F158" s="3"/>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G158" s="3"/>
+    </row>
+    <row r="159" spans="1:7">
       <c r="A159" s="1">
         <v>38384</v>
       </c>
       <c r="B159" s="4">
         <v>38426</v>
       </c>
-      <c r="C159" s="6">
+      <c r="C159" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D159" s="6">
         <v>325308</v>
       </c>
-      <c r="F159" s="3"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G159" s="3"/>
+    </row>
+    <row r="160" spans="1:7">
       <c r="A160" s="1">
         <v>38412</v>
       </c>
       <c r="B160" s="4">
         <v>38455</v>
       </c>
-      <c r="C160" s="6">
+      <c r="C160" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D160" s="6">
         <v>326179</v>
       </c>
-      <c r="F160" s="3"/>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G160" s="3"/>
+    </row>
+    <row r="161" spans="1:7">
       <c r="A161" s="1">
         <v>38443</v>
       </c>
       <c r="B161" s="4">
         <v>38484</v>
       </c>
-      <c r="C161" s="6">
+      <c r="C161" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D161" s="6">
         <v>329124</v>
       </c>
-      <c r="F161" s="3"/>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G161" s="3"/>
+    </row>
+    <row r="162" spans="1:7">
       <c r="A162" s="1">
         <v>38473</v>
       </c>
       <c r="B162" s="4">
         <v>38517</v>
       </c>
-      <c r="C162" s="6">
+      <c r="C162" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D162" s="6">
         <v>327233</v>
       </c>
-      <c r="F162" s="3"/>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G162" s="3"/>
+    </row>
+    <row r="163" spans="1:7">
       <c r="A163" s="1">
         <v>38504</v>
       </c>
       <c r="B163" s="4">
         <v>38547</v>
       </c>
-      <c r="C163" s="6">
+      <c r="C163" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D163" s="6">
         <v>337219</v>
       </c>
-      <c r="F163" s="3"/>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G163" s="3"/>
+    </row>
+    <row r="164" spans="1:7">
       <c r="A164" s="1">
         <v>38534</v>
       </c>
       <c r="B164" s="4">
         <v>38575</v>
       </c>
-      <c r="C164" s="6">
+      <c r="C164" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D164" s="6">
         <v>339529</v>
       </c>
-      <c r="F164" s="3"/>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G164" s="3"/>
+    </row>
+    <row r="165" spans="1:7">
       <c r="A165" s="1">
         <v>38565</v>
       </c>
       <c r="B165" s="4">
         <v>38609</v>
       </c>
-      <c r="C165" s="6">
+      <c r="C165" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D165" s="6">
         <v>335605</v>
       </c>
-      <c r="F165" s="3"/>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G165" s="3"/>
+    </row>
+    <row r="166" spans="1:7">
       <c r="A166" s="1">
         <v>38596</v>
       </c>
       <c r="B166" s="4">
         <v>38639</v>
       </c>
-      <c r="C166" s="6">
+      <c r="C166" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D166" s="6">
         <v>336600</v>
       </c>
-      <c r="F166" s="3"/>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G166" s="3"/>
+    </row>
+    <row r="167" spans="1:7">
       <c r="A167" s="1">
         <v>38626</v>
       </c>
       <c r="B167" s="4">
         <v>38671</v>
       </c>
-      <c r="C167" s="6">
+      <c r="C167" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D167" s="6">
         <v>336753</v>
       </c>
-      <c r="F167" s="3"/>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G167" s="3"/>
+    </row>
+    <row r="168" spans="1:7">
       <c r="A168" s="1">
         <v>38657</v>
       </c>
       <c r="B168" s="4">
         <v>38699</v>
       </c>
-      <c r="C168" s="6">
+      <c r="C168" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D168" s="6">
         <v>339719</v>
       </c>
-      <c r="F168" s="3"/>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G168" s="3"/>
+    </row>
+    <row r="169" spans="1:7">
       <c r="A169" s="1">
         <v>38687</v>
       </c>
       <c r="B169" s="4">
         <v>38730</v>
       </c>
-      <c r="C169" s="6">
+      <c r="C169" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D169" s="6">
         <v>339895</v>
       </c>
-      <c r="F169" s="3"/>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G169" s="3"/>
+    </row>
+    <row r="170" spans="1:7">
       <c r="A170" s="1">
         <v>38718</v>
       </c>
       <c r="B170" s="4">
         <v>38762</v>
       </c>
-      <c r="C170" s="6">
+      <c r="C170" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D170" s="6">
         <v>349664</v>
       </c>
-      <c r="F170" s="3"/>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G170" s="3"/>
+    </row>
+    <row r="171" spans="1:7">
       <c r="A171" s="1">
         <v>38749</v>
       </c>
       <c r="B171" s="4">
         <v>38790</v>
       </c>
-      <c r="C171" s="6">
+      <c r="C171" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D171" s="6">
         <v>347021</v>
       </c>
-      <c r="F171" s="3"/>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G171" s="3"/>
+    </row>
+    <row r="172" spans="1:7">
       <c r="A172" s="1">
         <v>38777</v>
       </c>
       <c r="B172" s="4">
         <v>38820</v>
       </c>
-      <c r="C172" s="6">
+      <c r="C172" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D172" s="6">
         <v>348357</v>
       </c>
-      <c r="F172" s="3"/>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G172" s="3"/>
+    </row>
+    <row r="173" spans="1:7">
       <c r="A173" s="1">
         <v>38808</v>
       </c>
       <c r="B173" s="4">
         <v>38848</v>
       </c>
-      <c r="C173" s="6">
+      <c r="C173" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D173" s="6">
         <v>350072</v>
       </c>
-      <c r="F173" s="3"/>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G173" s="3"/>
+    </row>
+    <row r="174" spans="1:7">
       <c r="A174" s="1">
         <v>38838</v>
       </c>
       <c r="B174" s="4">
         <v>38881</v>
       </c>
-      <c r="C174" s="6">
+      <c r="C174" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D174" s="6">
         <v>348889</v>
       </c>
-      <c r="F174" s="3"/>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G174" s="3"/>
+    </row>
+    <row r="175" spans="1:7">
       <c r="A175" s="1">
         <v>38869</v>
       </c>
       <c r="B175" s="4">
         <v>38912</v>
       </c>
-      <c r="C175" s="6">
+      <c r="C175" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D175" s="6">
         <v>350795</v>
       </c>
-      <c r="F175" s="3"/>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G175" s="3"/>
+    </row>
+    <row r="176" spans="1:7">
       <c r="A176" s="1">
         <v>38899</v>
       </c>
       <c r="B176" s="4">
         <v>38940</v>
       </c>
-      <c r="C176" s="6">
+      <c r="C176" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D176" s="6">
         <v>351916</v>
       </c>
-      <c r="F176" s="3"/>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G176" s="3"/>
+    </row>
+    <row r="177" spans="1:7">
       <c r="A177" s="1">
         <v>38930</v>
       </c>
       <c r="B177" s="4">
         <v>38974</v>
       </c>
-      <c r="C177" s="6">
+      <c r="C177" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D177" s="6">
         <v>353285</v>
       </c>
-      <c r="F177" s="3"/>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G177" s="3"/>
+    </row>
+    <row r="178" spans="1:7">
       <c r="A178" s="1">
         <v>38961</v>
       </c>
       <c r="B178" s="4">
         <v>39003</v>
       </c>
-      <c r="C178" s="6">
+      <c r="C178" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D178" s="6">
         <v>351240</v>
       </c>
-      <c r="F178" s="3"/>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G178" s="3"/>
+    </row>
+    <row r="179" spans="1:7">
       <c r="A179" s="1">
         <v>38991</v>
       </c>
       <c r="B179" s="4">
         <v>39035</v>
       </c>
-      <c r="C179" s="6">
+      <c r="C179" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D179" s="6">
         <v>351035</v>
       </c>
-      <c r="F179" s="3"/>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G179" s="3"/>
+    </row>
+    <row r="180" spans="1:7">
       <c r="A180" s="1">
         <v>39022</v>
       </c>
       <c r="B180" s="4">
         <v>39064</v>
       </c>
-      <c r="C180" s="6">
+      <c r="C180" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D180" s="6">
         <v>352116</v>
       </c>
-      <c r="F180" s="3"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G180" s="3"/>
+    </row>
+    <row r="181" spans="1:7">
       <c r="A181" s="1">
         <v>39052</v>
       </c>
       <c r="B181" s="4">
         <v>39094</v>
       </c>
-      <c r="C181" s="6">
+      <c r="C181" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D181" s="6">
         <v>356367</v>
       </c>
-      <c r="F181" s="3"/>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G181" s="3"/>
+    </row>
+    <row r="182" spans="1:7">
       <c r="A182" s="1">
         <v>39083</v>
       </c>
       <c r="B182" s="4">
         <v>39127</v>
       </c>
-      <c r="C182" s="6">
+      <c r="C182" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D182" s="6">
         <v>355792</v>
       </c>
-      <c r="F182" s="3"/>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G182" s="3"/>
+    </row>
+    <row r="183" spans="1:7">
       <c r="A183" s="1">
         <v>39114</v>
       </c>
       <c r="B183" s="4">
         <v>39154</v>
       </c>
-      <c r="C183" s="6">
+      <c r="C183" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D183" s="6">
         <v>356545</v>
       </c>
-      <c r="F183" s="3"/>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G183" s="3"/>
+    </row>
+    <row r="184" spans="1:7">
       <c r="A184" s="1">
         <v>39142</v>
       </c>
       <c r="B184" s="4">
         <v>39188</v>
       </c>
-      <c r="C184" s="6">
+      <c r="C184" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D184" s="6">
         <v>359415</v>
       </c>
-      <c r="F184" s="3"/>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G184" s="3"/>
+    </row>
+    <row r="185" spans="1:7">
       <c r="A185" s="1">
         <v>39173</v>
       </c>
       <c r="B185" s="4">
         <v>39213</v>
       </c>
-      <c r="C185" s="6">
+      <c r="C185" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D185" s="6">
         <v>358562</v>
       </c>
-      <c r="F185" s="3"/>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G185" s="3"/>
+    </row>
+    <row r="186" spans="1:7">
       <c r="A186" s="1">
         <v>39203</v>
       </c>
       <c r="B186" s="4">
         <v>39246</v>
       </c>
-      <c r="C186" s="6">
+      <c r="C186" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D186" s="6">
         <v>363085</v>
       </c>
-      <c r="F186" s="3"/>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G186" s="3"/>
+    </row>
+    <row r="187" spans="1:7">
       <c r="A187" s="1">
         <v>39234</v>
       </c>
       <c r="B187" s="4">
         <v>39276</v>
       </c>
-      <c r="C187" s="6">
+      <c r="C187" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D187" s="6">
         <v>360234</v>
       </c>
-      <c r="F187" s="3"/>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G187" s="3"/>
+    </row>
+    <row r="188" spans="1:7">
       <c r="A188" s="1">
         <v>39264</v>
       </c>
       <c r="B188" s="4">
         <v>39307</v>
       </c>
-      <c r="C188" s="6">
+      <c r="C188" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D188" s="6">
         <v>361770</v>
       </c>
-      <c r="F188" s="3"/>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G188" s="3"/>
+    </row>
+    <row r="189" spans="1:7">
       <c r="A189" s="1">
         <v>39295</v>
       </c>
       <c r="B189" s="4">
         <v>39339</v>
       </c>
-      <c r="C189" s="6">
+      <c r="C189" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D189" s="6">
         <v>363676</v>
       </c>
-      <c r="F189" s="3"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G189" s="3"/>
+    </row>
+    <row r="190" spans="1:7">
       <c r="A190" s="1">
         <v>39326</v>
       </c>
       <c r="B190" s="4">
         <v>39367</v>
       </c>
-      <c r="C190" s="6">
+      <c r="C190" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D190" s="6">
         <v>365178</v>
       </c>
-      <c r="F190" s="3"/>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G190" s="3"/>
+    </row>
+    <row r="191" spans="1:7">
       <c r="A191" s="1">
         <v>39356</v>
       </c>
       <c r="B191" s="4">
         <v>39400</v>
       </c>
-      <c r="C191" s="6">
+      <c r="C191" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D191" s="6">
         <v>367322</v>
       </c>
-      <c r="F191" s="3"/>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G191" s="3"/>
+    </row>
+    <row r="192" spans="1:7">
       <c r="A192" s="1">
         <v>39387</v>
       </c>
       <c r="B192" s="4">
         <v>39429</v>
       </c>
-      <c r="C192" s="6">
+      <c r="C192" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D192" s="6">
         <v>370776</v>
       </c>
-      <c r="F192" s="3"/>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G192" s="3"/>
+    </row>
+    <row r="193" spans="1:7">
       <c r="A193" s="1">
         <v>39417</v>
       </c>
       <c r="B193" s="4">
         <v>39462</v>
       </c>
-      <c r="C193" s="6">
+      <c r="C193" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D193" s="6">
         <v>366569</v>
       </c>
-      <c r="F193" s="3"/>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G193" s="3"/>
+    </row>
+    <row r="194" spans="1:7">
       <c r="A194" s="1">
         <v>39448</v>
       </c>
       <c r="B194" s="4">
         <v>39491</v>
       </c>
-      <c r="C194" s="6">
+      <c r="C194" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D194" s="6">
         <v>367368</v>
       </c>
-      <c r="F194" s="3"/>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G194" s="3"/>
+    </row>
+    <row r="195" spans="1:7">
       <c r="A195" s="1">
         <v>39479</v>
       </c>
       <c r="B195" s="4">
         <v>39520</v>
       </c>
-      <c r="C195" s="6">
+      <c r="C195" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D195" s="6">
         <v>364126</v>
       </c>
-      <c r="F195" s="3"/>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G195" s="3"/>
+    </row>
+    <row r="196" spans="1:7">
       <c r="A196" s="1">
         <v>39508</v>
       </c>
       <c r="B196" s="4">
         <v>39552</v>
       </c>
-      <c r="C196" s="6">
+      <c r="C196" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D196" s="6">
         <v>365164</v>
       </c>
-      <c r="F196" s="3"/>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G196" s="3"/>
+    </row>
+    <row r="197" spans="1:7">
       <c r="A197" s="1">
         <v>39539</v>
       </c>
       <c r="B197" s="4">
         <v>39581</v>
       </c>
-      <c r="C197" s="6">
+      <c r="C197" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D197" s="6">
         <v>364816</v>
       </c>
-      <c r="F197" s="3"/>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G197" s="3"/>
+    </row>
+    <row r="198" spans="1:7">
       <c r="A198" s="1">
         <v>39569</v>
       </c>
       <c r="B198" s="4">
         <v>39611</v>
       </c>
-      <c r="C198" s="6">
+      <c r="C198" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D198" s="6">
         <v>368255</v>
       </c>
-      <c r="F198" s="3"/>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G198" s="3"/>
+    </row>
+    <row r="199" spans="1:7">
       <c r="A199" s="1">
         <v>39600</v>
       </c>
       <c r="B199" s="4">
         <v>39644</v>
       </c>
-      <c r="C199" s="6">
+      <c r="C199" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D199" s="6">
         <v>368926</v>
       </c>
-      <c r="F199" s="3"/>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G199" s="3"/>
+    </row>
+    <row r="200" spans="1:7">
       <c r="A200" s="1">
         <v>39630</v>
       </c>
       <c r="B200" s="4">
         <v>39673</v>
       </c>
-      <c r="C200" s="6">
+      <c r="C200" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D200" s="6">
         <v>367594</v>
       </c>
-      <c r="F200" s="3"/>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G200" s="3"/>
+    </row>
+    <row r="201" spans="1:7">
       <c r="A201" s="1">
         <v>39661</v>
       </c>
       <c r="B201" s="4">
         <v>39703</v>
       </c>
-      <c r="C201" s="6">
+      <c r="C201" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D201" s="6">
         <v>364611</v>
       </c>
-      <c r="F201" s="3"/>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G201" s="3"/>
+    </row>
+    <row r="202" spans="1:7">
       <c r="A202" s="1">
         <v>39692</v>
       </c>
       <c r="B202" s="4">
         <v>39736</v>
       </c>
-      <c r="C202" s="6">
+      <c r="C202" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D202" s="6">
         <v>358991</v>
       </c>
-      <c r="F202" s="3"/>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G202" s="3"/>
+    </row>
+    <row r="203" spans="1:7">
       <c r="A203" s="1">
         <v>39722</v>
       </c>
       <c r="B203" s="4">
         <v>39766</v>
       </c>
-      <c r="C203" s="6">
+      <c r="C203" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D203" s="6">
         <v>346137</v>
       </c>
-      <c r="F203" s="3"/>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G203" s="3"/>
+    </row>
+    <row r="204" spans="1:7">
       <c r="A204" s="1">
         <v>39753</v>
       </c>
       <c r="B204" s="4">
         <v>39794</v>
       </c>
-      <c r="C204" s="6">
+      <c r="C204" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D204" s="6">
         <v>332498</v>
       </c>
-      <c r="F204" s="3"/>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G204" s="3"/>
+    </row>
+    <row r="205" spans="1:7">
       <c r="A205" s="1">
         <v>39783</v>
       </c>
       <c r="B205" s="4">
         <v>39827</v>
       </c>
-      <c r="C205" s="6">
+      <c r="C205" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D205" s="6">
         <v>324767</v>
       </c>
-      <c r="F205" s="3"/>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G205" s="3"/>
+    </row>
+    <row r="206" spans="1:7">
       <c r="A206" s="1">
         <v>39814</v>
       </c>
       <c r="B206" s="4">
         <v>39856</v>
       </c>
-      <c r="C206" s="6">
+      <c r="C206" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D206" s="6">
         <v>329787</v>
       </c>
-      <c r="F206" s="3"/>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G206" s="3"/>
+    </row>
+    <row r="207" spans="1:7">
       <c r="A207" s="1">
         <v>39845</v>
       </c>
       <c r="B207" s="4">
         <v>39884</v>
       </c>
-      <c r="C207" s="6">
+      <c r="C207" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D207" s="6">
         <v>328376</v>
       </c>
-      <c r="F207" s="3"/>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G207" s="3"/>
+    </row>
+    <row r="208" spans="1:7">
       <c r="A208" s="1">
         <v>39873</v>
       </c>
       <c r="B208" s="4">
         <v>39917</v>
       </c>
-      <c r="C208" s="6">
+      <c r="C208" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D208" s="6">
         <v>322634</v>
       </c>
-      <c r="F208" s="3"/>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G208" s="3"/>
+    </row>
+    <row r="209" spans="1:7">
       <c r="A209" s="1">
         <v>39904</v>
       </c>
       <c r="B209" s="4">
         <v>39946</v>
       </c>
-      <c r="C209" s="6">
+      <c r="C209" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D209" s="6">
         <v>324323</v>
       </c>
-      <c r="F209" s="3"/>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G209" s="3"/>
+    </row>
+    <row r="210" spans="1:7">
       <c r="A210" s="1">
         <v>39934</v>
       </c>
       <c r="B210" s="4">
         <v>39975</v>
       </c>
-      <c r="C210" s="6">
+      <c r="C210" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D210" s="6">
         <v>327011</v>
       </c>
-      <c r="F210" s="3"/>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G210" s="3"/>
+    </row>
+    <row r="211" spans="1:7">
       <c r="A211" s="1">
         <v>39965</v>
       </c>
       <c r="B211" s="4">
         <v>40008</v>
       </c>
-      <c r="C211" s="6">
+      <c r="C211" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D211" s="6">
         <v>332227</v>
       </c>
-      <c r="F211" s="3"/>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G211" s="3"/>
+    </row>
+    <row r="212" spans="1:7">
       <c r="A212" s="1">
         <v>39995</v>
       </c>
       <c r="B212" s="4">
         <v>40038</v>
       </c>
-      <c r="C212" s="6">
+      <c r="C212" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D212" s="6">
         <v>333670</v>
       </c>
-      <c r="F212" s="3"/>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G212" s="3"/>
+    </row>
+    <row r="213" spans="1:7">
       <c r="A213" s="1">
         <v>40026</v>
       </c>
       <c r="B213" s="4">
         <v>40071</v>
       </c>
-      <c r="C213" s="6">
+      <c r="C213" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D213" s="6">
         <v>339586</v>
       </c>
-      <c r="F213" s="3"/>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G213" s="3"/>
+    </row>
+    <row r="214" spans="1:7">
       <c r="A214" s="1">
         <v>40057</v>
       </c>
       <c r="B214" s="4">
         <v>40100</v>
       </c>
-      <c r="C214" s="6">
+      <c r="C214" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D214" s="6">
         <v>330998</v>
       </c>
-      <c r="F214" s="3"/>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G214" s="3"/>
+    </row>
+    <row r="215" spans="1:7">
       <c r="A215" s="1">
         <v>40087</v>
       </c>
       <c r="B215" s="4">
         <v>40133</v>
       </c>
-      <c r="C215" s="6">
+      <c r="C215" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D215" s="6">
         <v>334595</v>
       </c>
-      <c r="F215" s="3"/>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G215" s="3"/>
+    </row>
+    <row r="216" spans="1:7">
       <c r="A216" s="1">
         <v>40118</v>
       </c>
       <c r="B216" s="4">
         <v>40158</v>
       </c>
-      <c r="C216" s="6">
+      <c r="C216" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D216" s="6">
         <v>337321</v>
       </c>
-      <c r="F216" s="3"/>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G216" s="3"/>
+    </row>
+    <row r="217" spans="1:7">
       <c r="A217" s="1">
         <v>40148</v>
       </c>
       <c r="B217" s="4">
         <v>40192</v>
       </c>
-      <c r="C217" s="6">
+      <c r="C217" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D217" s="6">
         <v>338736</v>
       </c>
-      <c r="F217" s="3"/>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G217" s="3"/>
+    </row>
+    <row r="218" spans="1:7">
       <c r="A218" s="1">
         <v>40179</v>
       </c>
       <c r="B218" s="4">
         <v>40221</v>
       </c>
-      <c r="C218" s="6">
+      <c r="C218" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D218" s="6">
         <v>339093</v>
       </c>
-      <c r="F218" s="3"/>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G218" s="3"/>
+    </row>
+    <row r="219" spans="1:7">
       <c r="A219" s="1">
         <v>40210</v>
       </c>
       <c r="B219" s="4">
         <v>40249</v>
       </c>
-      <c r="C219" s="6">
+      <c r="C219" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D219" s="6">
         <v>339580</v>
       </c>
-      <c r="F219" s="3"/>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G219" s="3"/>
+    </row>
+    <row r="220" spans="1:7">
       <c r="A220" s="1">
         <v>40238</v>
       </c>
       <c r="B220" s="4">
         <v>40282</v>
       </c>
-      <c r="C220" s="6">
+      <c r="C220" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D220" s="6">
         <v>346974</v>
       </c>
-      <c r="F220" s="3"/>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G220" s="3"/>
+    </row>
+    <row r="221" spans="1:7">
       <c r="A221" s="1">
         <v>40269</v>
       </c>
       <c r="B221" s="4">
         <v>40312</v>
       </c>
-      <c r="C221" s="6">
+      <c r="C221" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D221" s="6">
         <v>349869</v>
       </c>
-      <c r="F221" s="3"/>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G221" s="3"/>
+    </row>
+    <row r="222" spans="1:7">
       <c r="A222" s="1">
         <v>40299</v>
       </c>
       <c r="B222" s="4">
         <v>40340</v>
       </c>
-      <c r="C222" s="6">
+      <c r="C222" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D222" s="6">
         <v>346858</v>
       </c>
-      <c r="F222" s="3"/>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G222" s="3"/>
+    </row>
+    <row r="223" spans="1:7">
       <c r="A223" s="1">
         <v>40330</v>
       </c>
       <c r="B223" s="4">
         <v>40373</v>
       </c>
-      <c r="C223" s="6">
+      <c r="C223" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D223" s="6">
         <v>346516</v>
       </c>
-      <c r="F223" s="3"/>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G223" s="3"/>
+    </row>
+    <row r="224" spans="1:7">
       <c r="A224" s="1">
         <v>40360</v>
       </c>
       <c r="B224" s="4">
         <v>40403</v>
       </c>
-      <c r="C224" s="6">
+      <c r="C224" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D224" s="6">
         <v>347612</v>
       </c>
-      <c r="F224" s="3"/>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G224" s="3"/>
+    </row>
+    <row r="225" spans="1:7">
       <c r="A225" s="1">
         <v>40391</v>
       </c>
       <c r="B225" s="4">
         <v>40435</v>
       </c>
-      <c r="C225" s="6">
+      <c r="C225" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D225" s="6">
         <v>349188</v>
       </c>
-      <c r="F225" s="3"/>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G225" s="3"/>
+    </row>
+    <row r="226" spans="1:7">
       <c r="A226" s="1">
         <v>40422</v>
       </c>
       <c r="B226" s="4">
         <v>40466</v>
       </c>
-      <c r="C226" s="6">
+      <c r="C226" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D226" s="6">
         <v>352179</v>
       </c>
-      <c r="F226" s="3"/>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G226" s="3"/>
+    </row>
+    <row r="227" spans="1:7">
       <c r="A227" s="1">
         <v>40452</v>
       </c>
       <c r="B227" s="4">
         <v>40497</v>
       </c>
-      <c r="C227" s="6">
+      <c r="C227" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D227" s="6">
         <v>356215</v>
       </c>
-      <c r="F227" s="3"/>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G227" s="3"/>
+    </row>
+    <row r="228" spans="1:7">
       <c r="A228" s="1">
         <v>40483</v>
       </c>
       <c r="B228" s="4">
         <v>40526</v>
       </c>
-      <c r="C228" s="6">
+      <c r="C228" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D228" s="6">
         <v>359450</v>
       </c>
-      <c r="F228" s="3"/>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G228" s="3"/>
+    </row>
+    <row r="229" spans="1:7">
       <c r="A229" s="1">
         <v>40513</v>
       </c>
       <c r="B229" s="4">
         <v>40557</v>
       </c>
-      <c r="C229" s="6">
+      <c r="C229" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D229" s="6">
         <v>361979</v>
       </c>
-      <c r="F229" s="3"/>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G229" s="3"/>
+    </row>
+    <row r="230" spans="1:7">
       <c r="A230" s="1">
         <v>40544</v>
       </c>
       <c r="B230" s="4">
         <v>40589</v>
       </c>
-      <c r="C230" s="6">
+      <c r="C230" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D230" s="6">
         <v>364394</v>
       </c>
-      <c r="F230" s="3"/>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G230" s="3"/>
+    </row>
+    <row r="231" spans="1:7">
       <c r="A231" s="1">
         <v>40575</v>
       </c>
       <c r="B231" s="4">
         <v>40613</v>
       </c>
-      <c r="C231" s="6">
+      <c r="C231" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D231" s="6">
         <v>367475</v>
       </c>
-      <c r="F231" s="3"/>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G231" s="3"/>
+    </row>
+    <row r="232" spans="1:7">
       <c r="A232" s="1">
         <v>40603</v>
       </c>
       <c r="B232" s="4">
         <v>40646</v>
       </c>
-      <c r="C232" s="6">
+      <c r="C232" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D232" s="6">
         <v>370775</v>
       </c>
-      <c r="F232" s="3"/>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G232" s="3"/>
+    </row>
+    <row r="233" spans="1:7">
       <c r="A233" s="1">
         <v>40634</v>
       </c>
       <c r="B233" s="4">
         <v>40675</v>
       </c>
-      <c r="C233" s="6">
+      <c r="C233" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D233" s="6">
         <v>372820</v>
       </c>
-      <c r="F233" s="3"/>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G233" s="3"/>
+    </row>
+    <row r="234" spans="1:7">
       <c r="A234" s="1">
         <v>40664</v>
       </c>
       <c r="B234" s="4">
         <v>40708</v>
       </c>
-      <c r="C234" s="6">
+      <c r="C234" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D234" s="6">
         <v>372505</v>
       </c>
-      <c r="F234" s="3"/>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G234" s="3"/>
+    </row>
+    <row r="235" spans="1:7">
       <c r="A235" s="1">
         <v>40695</v>
       </c>
       <c r="B235" s="4">
         <v>40738</v>
       </c>
-      <c r="C235" s="6">
+      <c r="C235" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D235" s="6">
         <v>375587</v>
       </c>
-      <c r="F235" s="3"/>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G235" s="3"/>
+    </row>
+    <row r="236" spans="1:7">
       <c r="A236" s="1">
         <v>40725</v>
       </c>
       <c r="B236" s="4">
         <v>40767</v>
       </c>
-      <c r="C236" s="6">
+      <c r="C236" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D236" s="6">
         <v>375442</v>
       </c>
-      <c r="F236" s="3"/>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G236" s="3"/>
+    </row>
+    <row r="237" spans="1:7">
       <c r="A237" s="1">
         <v>40756</v>
       </c>
       <c r="B237" s="4">
         <v>40800</v>
       </c>
-      <c r="C237" s="6">
+      <c r="C237" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D237" s="6">
         <v>375860</v>
       </c>
-      <c r="F237" s="3"/>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G237" s="3"/>
+    </row>
+    <row r="238" spans="1:7">
       <c r="A238" s="1">
         <v>40787</v>
       </c>
       <c r="B238" s="4">
         <v>40830</v>
       </c>
-      <c r="C238" s="6">
+      <c r="C238" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D238" s="6">
         <v>380042</v>
       </c>
-      <c r="F238" s="3"/>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G238" s="3"/>
+    </row>
+    <row r="239" spans="1:7">
       <c r="A239" s="1">
         <v>40817</v>
       </c>
       <c r="B239" s="4">
         <v>40862</v>
       </c>
-      <c r="C239" s="6">
+      <c r="C239" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D239" s="6">
         <v>382207</v>
       </c>
-      <c r="F239" s="3"/>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G239" s="3"/>
+    </row>
+    <row r="240" spans="1:7">
       <c r="A240" s="1">
         <v>40848</v>
       </c>
       <c r="B240" s="4">
         <v>40890</v>
       </c>
-      <c r="C240" s="6">
+      <c r="C240" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D240" s="6">
         <v>383422</v>
       </c>
-      <c r="F240" s="3"/>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G240" s="3"/>
+    </row>
+    <row r="241" spans="1:7">
       <c r="A241" s="1">
         <v>40878</v>
       </c>
       <c r="B241" s="4">
         <v>40920</v>
       </c>
-      <c r="C241" s="6">
+      <c r="C241" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D241" s="6">
         <v>383985</v>
       </c>
-      <c r="F241" s="3"/>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G241" s="3"/>
+    </row>
+    <row r="242" spans="1:7">
       <c r="A242" s="1">
         <v>40909</v>
       </c>
       <c r="B242" s="4">
         <v>40953</v>
       </c>
-      <c r="C242" s="6">
+      <c r="C242" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D242" s="6">
         <v>387531</v>
       </c>
-      <c r="F242" s="3"/>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G242" s="3"/>
+    </row>
+    <row r="243" spans="1:7">
       <c r="A243" s="1">
         <v>40940</v>
       </c>
       <c r="B243" s="4">
         <v>40981</v>
       </c>
-      <c r="C243" s="6">
+      <c r="C243" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D243" s="6">
         <v>392310</v>
       </c>
-      <c r="F243" s="3"/>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G243" s="3"/>
+    </row>
+    <row r="244" spans="1:7">
       <c r="A244" s="1">
         <v>40969</v>
       </c>
       <c r="B244" s="4">
         <v>41015</v>
       </c>
-      <c r="C244" s="6">
+      <c r="C244" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D244" s="6">
         <v>393698</v>
       </c>
-      <c r="F244" s="3"/>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G244" s="3"/>
+    </row>
+    <row r="245" spans="1:7">
       <c r="A245" s="1">
         <v>41000</v>
       </c>
       <c r="B245" s="4">
         <v>41044</v>
       </c>
-      <c r="C245" s="6">
+      <c r="C245" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D245" s="6">
         <v>392073</v>
       </c>
-      <c r="F245" s="3"/>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G245" s="3"/>
+    </row>
+    <row r="246" spans="1:7">
       <c r="A246" s="1">
         <v>41030</v>
       </c>
       <c r="B246" s="4">
         <v>41073</v>
       </c>
-      <c r="C246" s="6">
+      <c r="C246" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D246" s="6">
         <v>391376</v>
       </c>
-      <c r="F246" s="3"/>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G246" s="3"/>
+    </row>
+    <row r="247" spans="1:7">
       <c r="A247" s="1">
         <v>41061</v>
       </c>
       <c r="B247" s="4">
         <v>41106</v>
       </c>
-      <c r="C247" s="6">
+      <c r="C247" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D247" s="6">
         <v>387901</v>
       </c>
-      <c r="F247" s="3"/>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G247" s="3"/>
+    </row>
+    <row r="248" spans="1:7">
       <c r="A248" s="1">
         <v>41091</v>
       </c>
       <c r="B248" s="4">
         <v>41135</v>
       </c>
-      <c r="C248" s="6">
+      <c r="C248" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D248" s="6">
         <v>389686</v>
       </c>
-      <c r="F248" s="3"/>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G248" s="3"/>
+    </row>
+    <row r="249" spans="1:7">
       <c r="A249" s="1">
         <v>41122</v>
       </c>
       <c r="B249" s="4">
         <v>41166</v>
       </c>
-      <c r="C249" s="6">
+      <c r="C249" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D249" s="6">
         <v>394524</v>
       </c>
-      <c r="F249" s="3"/>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G249" s="3"/>
+    </row>
+    <row r="250" spans="1:7">
       <c r="A250" s="1">
         <v>41153</v>
       </c>
       <c r="B250" s="4">
         <v>41197</v>
       </c>
-      <c r="C250" s="6">
+      <c r="C250" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D250" s="6">
         <v>397681</v>
       </c>
-      <c r="F250" s="3"/>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G250" s="3"/>
+    </row>
+    <row r="251" spans="1:7">
       <c r="A251" s="1">
         <v>41183</v>
       </c>
       <c r="B251" s="4">
         <v>41227</v>
       </c>
-      <c r="C251" s="6">
+      <c r="C251" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D251" s="6">
         <v>397494</v>
       </c>
-      <c r="F251" s="3"/>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G251" s="3"/>
+    </row>
+    <row r="252" spans="1:7">
       <c r="A252" s="1">
         <v>41214</v>
       </c>
       <c r="B252" s="4">
         <v>41256</v>
       </c>
-      <c r="C252" s="6">
+      <c r="C252" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D252" s="6">
         <v>399708</v>
       </c>
-      <c r="F252" s="3"/>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G252" s="3"/>
+    </row>
+    <row r="253" spans="1:7">
       <c r="A253" s="1">
         <v>41244</v>
       </c>
       <c r="B253" s="4">
         <v>41289</v>
       </c>
-      <c r="C253" s="6">
+      <c r="C253" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D253" s="6">
         <v>401093</v>
       </c>
-      <c r="F253" s="3"/>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G253" s="3"/>
+    </row>
+    <row r="254" spans="1:7">
       <c r="A254" s="1">
         <v>41275</v>
       </c>
       <c r="B254" s="4">
         <v>41318</v>
       </c>
-      <c r="C254" s="6">
+      <c r="C254" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D254" s="6">
         <v>404434</v>
       </c>
-      <c r="F254" s="3"/>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G254" s="3"/>
+    </row>
+    <row r="255" spans="1:7">
       <c r="A255" s="1">
         <v>41306</v>
       </c>
       <c r="B255" s="4">
         <v>41346</v>
       </c>
-      <c r="C255" s="6">
+      <c r="C255" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D255" s="6">
         <v>409118</v>
       </c>
-      <c r="F255" s="3"/>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G255" s="3"/>
+    </row>
+    <row r="256" spans="1:7">
       <c r="A256" s="1">
         <v>41334</v>
       </c>
       <c r="B256" s="4">
         <v>41376</v>
       </c>
-      <c r="C256" s="6">
+      <c r="C256" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D256" s="6">
         <v>406223</v>
       </c>
-      <c r="F256" s="3"/>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G256" s="3"/>
+    </row>
+    <row r="257" spans="1:7">
       <c r="A257" s="1">
         <v>41365</v>
       </c>
       <c r="B257" s="4">
         <v>41407</v>
       </c>
-      <c r="C257" s="6">
+      <c r="C257" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D257" s="6">
         <v>404231</v>
       </c>
-      <c r="F257" s="3"/>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G257" s="3"/>
+    </row>
+    <row r="258" spans="1:7">
       <c r="A258" s="1">
         <v>41395</v>
       </c>
       <c r="B258" s="4">
         <v>41438</v>
       </c>
-      <c r="C258" s="6">
+      <c r="C258" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D258" s="6">
         <v>406677</v>
       </c>
-      <c r="F258" s="3"/>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G258" s="3"/>
+    </row>
+    <row r="259" spans="1:7">
       <c r="A259" s="1">
         <v>41426</v>
       </c>
       <c r="B259" s="4">
         <v>41470</v>
       </c>
-      <c r="C259" s="6">
+      <c r="C259" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D259" s="6">
         <v>407921</v>
       </c>
-      <c r="F259" s="3"/>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G259" s="3"/>
+    </row>
+    <row r="260" spans="1:7">
       <c r="A260" s="1">
         <v>41456</v>
       </c>
       <c r="B260" s="4">
         <v>41499</v>
       </c>
-      <c r="C260" s="6">
+      <c r="C260" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D260" s="6">
         <v>410268</v>
       </c>
-      <c r="F260" s="3"/>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G260" s="3"/>
+    </row>
+    <row r="261" spans="1:7">
       <c r="A261" s="1">
         <v>41487</v>
       </c>
       <c r="B261" s="4">
         <v>41530</v>
       </c>
-      <c r="C261" s="6">
+      <c r="C261" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D261" s="6">
         <v>409691</v>
       </c>
-      <c r="F261" s="3"/>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G261" s="3"/>
+    </row>
+    <row r="262" spans="1:7">
       <c r="A262" s="1">
         <v>41518</v>
       </c>
       <c r="B262" s="4">
         <v>41576</v>
       </c>
-      <c r="C262" s="6">
+      <c r="C262" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D262" s="6">
         <v>410044</v>
       </c>
-      <c r="F262" s="3"/>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G262" s="3"/>
+    </row>
+    <row r="263" spans="1:7">
       <c r="A263" s="1">
         <v>41548</v>
       </c>
       <c r="B263" s="4">
         <v>41598</v>
       </c>
-      <c r="C263" s="6">
+      <c r="C263" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D263" s="6">
         <v>411399</v>
       </c>
-      <c r="F263" s="3"/>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G263" s="3"/>
+    </row>
+    <row r="264" spans="1:7">
       <c r="A264" s="1">
         <v>41579</v>
       </c>
       <c r="B264" s="4">
         <v>41620</v>
       </c>
-      <c r="C264" s="6">
+      <c r="C264" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D264" s="6">
         <v>412561</v>
       </c>
-      <c r="F264" s="3"/>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G264" s="3"/>
+    </row>
+    <row r="265" spans="1:7">
       <c r="A265" s="1">
         <v>41609</v>
       </c>
       <c r="B265" s="4">
         <v>41653</v>
       </c>
-      <c r="C265" s="6">
+      <c r="C265" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D265" s="6">
         <v>414812</v>
       </c>
-      <c r="F265" s="3"/>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G265" s="3"/>
+    </row>
+    <row r="266" spans="1:7">
       <c r="A266" s="1">
         <v>41640</v>
       </c>
       <c r="B266" s="4">
         <v>41683</v>
       </c>
-      <c r="C266" s="6">
+      <c r="C266" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D266" s="6">
         <v>411561</v>
       </c>
-      <c r="F266" s="3"/>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G266" s="3"/>
+    </row>
+    <row r="267" spans="1:7">
       <c r="A267" s="1">
         <v>41671</v>
       </c>
       <c r="B267" s="4">
         <v>41711</v>
       </c>
-      <c r="C267" s="6">
+      <c r="C267" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D267" s="6">
         <v>416736</v>
       </c>
-      <c r="F267" s="3"/>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G267" s="3"/>
+    </row>
+    <row r="268" spans="1:7">
       <c r="A268" s="1">
         <v>41699</v>
       </c>
       <c r="B268" s="4">
         <v>41743</v>
       </c>
-      <c r="C268" s="6">
+      <c r="C268" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D268" s="6">
         <v>421230</v>
       </c>
-      <c r="F268" s="3"/>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G268" s="3"/>
+    </row>
+    <row r="269" spans="1:7">
       <c r="A269" s="1">
         <v>41730</v>
       </c>
       <c r="B269" s="4">
         <v>41772</v>
       </c>
-      <c r="C269" s="6">
+      <c r="C269" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D269" s="6">
         <v>425546</v>
       </c>
-      <c r="F269" s="3"/>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G269" s="3"/>
+    </row>
+    <row r="270" spans="1:7">
       <c r="A270" s="1">
         <v>41760</v>
       </c>
       <c r="B270" s="4">
         <v>41802</v>
       </c>
-      <c r="C270" s="6">
+      <c r="C270" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D270" s="6">
         <v>426253</v>
       </c>
-      <c r="F270" s="3"/>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G270" s="3"/>
+    </row>
+    <row r="271" spans="1:7">
       <c r="A271" s="1">
         <v>41791</v>
       </c>
       <c r="B271" s="4">
         <v>41835</v>
       </c>
-      <c r="C271" s="6">
+      <c r="C271" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D271" s="6">
         <v>427305</v>
       </c>
-      <c r="F271" s="3"/>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G271" s="3"/>
+    </row>
+    <row r="272" spans="1:7">
       <c r="A272" s="1">
         <v>41821</v>
       </c>
       <c r="B272" s="4">
         <v>41864</v>
       </c>
-      <c r="C272" s="6">
+      <c r="C272" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D272" s="6">
         <v>428079</v>
       </c>
-      <c r="F272" s="3"/>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G272" s="3"/>
+    </row>
+    <row r="273" spans="1:7">
       <c r="A273" s="1">
         <v>41852</v>
       </c>
       <c r="B273" s="4">
         <v>41894</v>
       </c>
-      <c r="C273" s="6">
+      <c r="C273" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D273" s="6">
         <v>431379</v>
       </c>
-      <c r="F273" s="3"/>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G273" s="3"/>
+    </row>
+    <row r="274" spans="1:7">
       <c r="A274" s="1">
         <v>41883</v>
       </c>
       <c r="B274" s="4">
         <v>41927</v>
       </c>
-      <c r="C274" s="6">
+      <c r="C274" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D274" s="6">
         <v>430189</v>
       </c>
-      <c r="F274" s="3"/>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G274" s="3"/>
+    </row>
+    <row r="275" spans="1:7">
       <c r="A275" s="1">
         <v>41913</v>
       </c>
       <c r="B275" s="4">
         <v>41957</v>
       </c>
-      <c r="C275" s="6">
+      <c r="C275" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D275" s="6">
         <v>431903</v>
       </c>
-      <c r="F275" s="3"/>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G275" s="3"/>
+    </row>
+    <row r="276" spans="1:7">
       <c r="A276" s="1">
         <v>41944</v>
       </c>
       <c r="B276" s="4">
         <v>41984</v>
       </c>
-      <c r="C276" s="6">
+      <c r="C276" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D276" s="6">
         <v>433113</v>
       </c>
-      <c r="F276" s="3"/>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G276" s="3"/>
+    </row>
+    <row r="277" spans="1:7">
       <c r="A277" s="1">
         <v>41974</v>
       </c>
       <c r="B277" s="4">
         <v>42018</v>
       </c>
-      <c r="C277" s="6">
+      <c r="C277" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D277" s="6">
         <v>430110</v>
       </c>
-      <c r="F277" s="3"/>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G277" s="3"/>
+    </row>
+    <row r="278" spans="1:7">
       <c r="A278" s="1">
         <v>42005</v>
       </c>
       <c r="B278" s="4">
         <v>42047</v>
       </c>
-      <c r="C278" s="6">
+      <c r="C278" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D278" s="6">
         <v>428208</v>
       </c>
-      <c r="F278" s="3"/>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G278" s="3"/>
+    </row>
+    <row r="279" spans="1:7">
       <c r="A279" s="1">
         <v>42036</v>
       </c>
       <c r="B279" s="4">
         <v>42075</v>
       </c>
-      <c r="C279" s="6">
+      <c r="C279" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D279" s="6">
         <v>427119</v>
       </c>
-      <c r="F279" s="3"/>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G279" s="3"/>
+    </row>
+    <row r="280" spans="1:7">
       <c r="A280" s="1">
         <v>42064</v>
       </c>
       <c r="B280" s="4">
         <v>42108</v>
       </c>
-      <c r="C280" s="6">
+      <c r="C280" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D280" s="6">
         <v>433647</v>
       </c>
-      <c r="F280" s="3"/>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G280" s="3"/>
+    </row>
+    <row r="281" spans="1:7">
       <c r="A281" s="1">
         <v>42095</v>
       </c>
       <c r="B281" s="4">
         <v>42137</v>
       </c>
-      <c r="C281" s="6">
+      <c r="C281" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D281" s="6">
         <v>434470</v>
       </c>
-      <c r="F281" s="3"/>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G281" s="3"/>
+    </row>
+    <row r="282" spans="1:7">
       <c r="A282" s="1">
         <v>42125</v>
       </c>
       <c r="B282" s="4">
         <v>42166</v>
       </c>
-      <c r="C282" s="6">
+      <c r="C282" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D282" s="6">
         <v>437865</v>
       </c>
-      <c r="F282" s="3"/>
-    </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G282" s="3"/>
+    </row>
+    <row r="283" spans="1:7">
       <c r="A283" s="1">
         <v>42156</v>
       </c>
       <c r="B283" s="4">
         <v>42199</v>
       </c>
-      <c r="C283" s="6">
+      <c r="C283" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D283" s="6">
         <v>437951</v>
       </c>
-      <c r="F283" s="3"/>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G283" s="3"/>
+    </row>
+    <row r="284" spans="1:7">
       <c r="A284" s="1">
         <v>42186</v>
       </c>
       <c r="B284" s="4">
         <v>42229</v>
       </c>
-      <c r="C284" s="6">
+      <c r="C284" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D284" s="6">
         <v>441942</v>
       </c>
-      <c r="F284" s="3"/>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G284" s="3"/>
+    </row>
+    <row r="285" spans="1:7">
       <c r="A285" s="1">
         <v>42217</v>
       </c>
       <c r="B285" s="4">
         <v>42262</v>
       </c>
-      <c r="C285" s="6">
+      <c r="C285" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D285" s="6">
         <v>441849</v>
       </c>
-      <c r="F285" s="3"/>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G285" s="3"/>
+    </row>
+    <row r="286" spans="1:7">
       <c r="A286" s="1">
         <v>42248</v>
       </c>
       <c r="B286" s="4">
         <v>42291</v>
       </c>
-      <c r="C286" s="6">
+      <c r="C286" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D286" s="6">
         <v>439867</v>
       </c>
-      <c r="F286" s="3"/>
-    </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G286" s="3"/>
+    </row>
+    <row r="287" spans="1:7">
       <c r="A287" s="1">
         <v>42278</v>
       </c>
       <c r="B287" s="4">
         <v>42321</v>
       </c>
-      <c r="C287" s="6">
+      <c r="C287" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D287" s="6">
         <v>438693</v>
       </c>
-      <c r="F287" s="3"/>
-    </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G287" s="3"/>
+    </row>
+    <row r="288" spans="1:7">
       <c r="A288" s="1">
         <v>42309</v>
       </c>
       <c r="B288" s="4">
         <v>42349</v>
       </c>
-      <c r="C288" s="6">
+      <c r="C288" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D288" s="6">
         <v>440303</v>
       </c>
-      <c r="F288" s="3"/>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G288" s="3"/>
+    </row>
+    <row r="289" spans="1:7">
       <c r="A289" s="1">
         <v>42339</v>
       </c>
       <c r="B289" s="4">
         <v>42384</v>
       </c>
-      <c r="C289" s="6">
+      <c r="C289" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D289" s="6">
         <v>442149</v>
       </c>
-      <c r="F289" s="3"/>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G289" s="3"/>
+    </row>
+    <row r="290" spans="1:7">
       <c r="A290" s="1">
         <v>42370</v>
       </c>
       <c r="B290" s="4">
         <v>42412</v>
       </c>
-      <c r="C290" s="6">
+      <c r="C290" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D290" s="6">
         <v>439466</v>
       </c>
-      <c r="F290" s="3"/>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G290" s="3"/>
+    </row>
+    <row r="291" spans="1:7">
       <c r="A291" s="1">
         <v>42401</v>
       </c>
       <c r="B291" s="4">
         <v>42444</v>
       </c>
-      <c r="C291" s="6">
+      <c r="C291" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D291" s="6">
         <v>443117</v>
       </c>
-      <c r="F291" s="3"/>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G291" s="3"/>
+    </row>
+    <row r="292" spans="1:7">
       <c r="A292" s="1">
         <v>42430</v>
       </c>
       <c r="B292" s="4">
         <v>42473</v>
       </c>
-      <c r="C292" s="6">
+      <c r="C292" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D292" s="6">
         <v>441856</v>
       </c>
-      <c r="F292" s="3"/>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G292" s="3"/>
+    </row>
+    <row r="293" spans="1:7">
       <c r="A293" s="1">
         <v>42461</v>
       </c>
       <c r="B293" s="4">
         <v>42503</v>
       </c>
-      <c r="C293" s="6">
+      <c r="C293" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D293" s="6">
         <v>444254</v>
       </c>
-      <c r="F293" s="3"/>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G293" s="3"/>
+    </row>
+    <row r="294" spans="1:7">
       <c r="A294" s="1">
         <v>42491</v>
       </c>
       <c r="B294" s="4">
         <v>42535</v>
       </c>
-      <c r="C294" s="6">
+      <c r="C294" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D294" s="6">
         <v>445490</v>
       </c>
-      <c r="F294" s="3"/>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G294" s="3"/>
+    </row>
+    <row r="295" spans="1:7">
       <c r="A295" s="1">
         <v>42522</v>
       </c>
       <c r="B295" s="4">
         <v>42566</v>
       </c>
-      <c r="C295" s="6">
+      <c r="C295" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D295" s="6">
         <v>450237</v>
       </c>
-      <c r="F295" s="3"/>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G295" s="3"/>
+    </row>
+    <row r="296" spans="1:7">
       <c r="A296" s="1">
         <v>42552</v>
       </c>
       <c r="B296" s="4">
         <v>42594</v>
       </c>
-      <c r="C296" s="6">
+      <c r="C296" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D296" s="6">
         <v>449789</v>
       </c>
-      <c r="F296" s="3"/>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G296" s="3"/>
+    </row>
+    <row r="297" spans="1:7">
       <c r="A297" s="1">
         <v>42583</v>
       </c>
       <c r="B297" s="4">
         <v>42628</v>
       </c>
-      <c r="C297" s="6">
+      <c r="C297" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D297" s="6">
         <v>449946</v>
       </c>
-      <c r="F297" s="3"/>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G297" s="3"/>
+    </row>
+    <row r="298" spans="1:7">
       <c r="A298" s="1">
         <v>42614</v>
       </c>
       <c r="B298" s="4">
         <v>42657</v>
       </c>
-      <c r="C298" s="6">
+      <c r="C298" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D298" s="6">
         <v>453056</v>
       </c>
-      <c r="F298" s="3"/>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G298" s="3"/>
+    </row>
+    <row r="299" spans="1:7">
       <c r="A299" s="1">
         <v>42644</v>
       </c>
       <c r="B299" s="4">
         <v>42689</v>
       </c>
-      <c r="C299" s="6">
+      <c r="C299" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D299" s="6">
         <v>453847</v>
       </c>
-      <c r="F299" s="3"/>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G299" s="3"/>
+    </row>
+    <row r="300" spans="1:7">
       <c r="A300" s="1">
         <v>42675</v>
       </c>
       <c r="B300" s="4">
         <v>42718</v>
       </c>
-      <c r="C300" s="6">
+      <c r="C300" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D300" s="6">
         <v>453892</v>
       </c>
-      <c r="F300" s="3"/>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G300" s="3"/>
+    </row>
+    <row r="301" spans="1:7">
       <c r="A301" s="1">
         <v>42705</v>
       </c>
       <c r="B301" s="4">
         <v>42748</v>
       </c>
-      <c r="C301" s="6">
+      <c r="C301" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D301" s="6">
         <v>459305</v>
       </c>
-      <c r="F301" s="3"/>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G301" s="3"/>
+    </row>
+    <row r="302" spans="1:7">
       <c r="A302" s="1">
         <v>42736</v>
       </c>
       <c r="B302" s="4">
         <v>42781</v>
       </c>
-      <c r="C302" s="6">
+      <c r="C302" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D302" s="6">
         <v>464412</v>
       </c>
-      <c r="F302" s="3"/>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G302" s="3"/>
+    </row>
+    <row r="303" spans="1:7">
       <c r="A303" s="1">
         <v>42767</v>
       </c>
       <c r="B303" s="4">
         <v>42809</v>
       </c>
-      <c r="C303" s="6">
+      <c r="C303" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D303" s="6">
         <v>464284</v>
       </c>
-      <c r="F303" s="3"/>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G303" s="3"/>
+    </row>
+    <row r="304" spans="1:7">
       <c r="A304" s="1">
         <v>42795</v>
       </c>
       <c r="B304" s="4">
         <v>42839</v>
       </c>
-      <c r="C304" s="6">
+      <c r="C304" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D304" s="6">
         <v>463674</v>
       </c>
-      <c r="F304" s="3"/>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G304" s="3"/>
+    </row>
+    <row r="305" spans="1:7">
       <c r="A305" s="1">
         <v>42826</v>
       </c>
       <c r="B305" s="4">
         <v>42867</v>
       </c>
-      <c r="C305" s="6">
+      <c r="C305" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D305" s="6">
         <v>465276</v>
       </c>
-      <c r="F305" s="3"/>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G305" s="3"/>
+    </row>
+    <row r="306" spans="1:7">
       <c r="A306" s="1">
         <v>42856</v>
       </c>
       <c r="B306" s="4">
         <v>42900</v>
       </c>
-      <c r="C306" s="6">
+      <c r="C306" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D306" s="6">
         <v>462754</v>
       </c>
-      <c r="F306" s="3"/>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G306" s="3"/>
+    </row>
+    <row r="307" spans="1:7">
       <c r="A307" s="1">
         <v>42887</v>
       </c>
       <c r="B307" s="4">
         <v>42930</v>
       </c>
-      <c r="C307" s="6">
+      <c r="C307" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D307" s="6">
         <v>465130</v>
       </c>
-      <c r="F307" s="3"/>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G307" s="3"/>
+    </row>
+    <row r="308" spans="1:7">
       <c r="A308" s="1">
         <v>42917</v>
       </c>
       <c r="B308" s="4">
         <v>42962</v>
       </c>
-      <c r="C308" s="6">
+      <c r="C308" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D308" s="6">
         <v>465089</v>
       </c>
-      <c r="F308" s="3"/>
-    </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G308" s="3"/>
+    </row>
+    <row r="309" spans="1:7">
       <c r="A309" s="1">
         <v>42948</v>
       </c>
       <c r="B309" s="4">
         <v>42993</v>
       </c>
-      <c r="C309" s="6">
+      <c r="C309" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D309" s="6">
         <v>466020</v>
       </c>
-      <c r="F309" s="3"/>
-    </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G309" s="3"/>
+    </row>
+    <row r="310" spans="1:7">
       <c r="A310" s="1">
         <v>42979</v>
       </c>
       <c r="B310" s="4">
         <v>43021</v>
       </c>
-      <c r="C310" s="6">
+      <c r="C310" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D310" s="6">
         <v>475724</v>
       </c>
-      <c r="F310" s="3"/>
-    </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G310" s="3"/>
+    </row>
+    <row r="311" spans="1:7">
       <c r="A311" s="1">
         <v>43009</v>
       </c>
       <c r="B311" s="4">
         <v>43054</v>
       </c>
-      <c r="C311" s="6">
+      <c r="C311" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D311" s="6">
         <v>476107</v>
       </c>
-      <c r="F311" s="3"/>
-    </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G311" s="3"/>
+    </row>
+    <row r="312" spans="1:7">
       <c r="A312" s="1">
         <v>43040</v>
       </c>
       <c r="B312" s="4">
         <v>43083</v>
       </c>
-      <c r="C312" s="6">
+      <c r="C312" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D312" s="6">
         <v>480949</v>
       </c>
-      <c r="F312" s="3"/>
-    </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G312" s="3"/>
+    </row>
+    <row r="313" spans="1:7">
       <c r="A313" s="1">
         <v>43070</v>
       </c>
       <c r="B313" s="4">
         <v>43112</v>
       </c>
-      <c r="C313" s="6">
+      <c r="C313" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D313" s="6">
         <v>483586</v>
       </c>
-      <c r="F313" s="3"/>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G313" s="3"/>
+    </row>
+    <row r="314" spans="1:7">
       <c r="A314" s="1">
         <v>43101</v>
       </c>
       <c r="B314" s="4">
         <v>43145</v>
       </c>
-      <c r="C314" s="6">
+      <c r="C314" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D314" s="6">
         <v>481414</v>
       </c>
-      <c r="F314" s="3"/>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G314" s="3"/>
+    </row>
+    <row r="315" spans="1:7">
       <c r="A315" s="1">
         <v>43132</v>
       </c>
       <c r="B315" s="4">
         <v>43173</v>
       </c>
-      <c r="C315" s="6">
+      <c r="C315" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D315" s="6">
         <v>484031</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7">
       <c r="A316" s="1">
         <v>43160</v>
       </c>
       <c r="B316" s="4">
         <v>43206</v>
       </c>
-      <c r="C316" s="6">
+      <c r="C316" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D316" s="6">
         <v>484110</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7">
       <c r="A317" s="1">
         <v>43191</v>
       </c>
       <c r="B317" s="4">
         <v>43235</v>
       </c>
-      <c r="C317" s="6">
+      <c r="C317" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D317" s="6">
         <v>484154</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7">
       <c r="A318" s="1">
         <v>43221</v>
       </c>
       <c r="B318" s="4">
         <v>43265</v>
       </c>
-      <c r="C318" s="6">
+      <c r="C318" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D318" s="6">
         <v>491960</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7">
       <c r="A319" s="1">
         <v>43252</v>
       </c>
       <c r="B319" s="4">
         <v>43297</v>
       </c>
-      <c r="C319" s="6">
+      <c r="C319" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D319" s="6">
         <v>490228</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7">
       <c r="A320" s="1">
         <v>43282</v>
       </c>
       <c r="B320" s="4">
         <v>43327</v>
       </c>
-      <c r="C320" s="6">
+      <c r="C320" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D320" s="6">
         <v>493142</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4">
       <c r="A321" s="1">
         <v>43313</v>
       </c>
       <c r="B321" s="4">
         <v>43357</v>
       </c>
-      <c r="C321" s="6">
+      <c r="C321" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D321" s="6">
         <v>493445</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4">
       <c r="A322" s="1">
         <v>43344</v>
       </c>
       <c r="B322" s="4">
         <v>43388</v>
       </c>
-      <c r="C322" s="6">
+      <c r="C322" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D322" s="6">
         <v>491507</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4">
       <c r="A323" s="1">
         <v>43374</v>
       </c>
       <c r="B323" s="4">
         <v>43419</v>
       </c>
-      <c r="C323" s="6">
+      <c r="C323" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D323" s="6">
         <v>496416</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4">
       <c r="A324" s="1">
         <v>43405</v>
       </c>
       <c r="B324" s="4">
         <v>43448</v>
       </c>
-      <c r="C324" s="6">
+      <c r="C324" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D324" s="6">
         <v>498854</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4">
       <c r="A325" s="1">
         <v>43435</v>
       </c>
       <c r="B325" s="4">
         <v>43510</v>
       </c>
-      <c r="C325" s="6">
+      <c r="C325" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D325" s="6">
         <v>489113</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4">
       <c r="A326" s="1">
         <v>43466</v>
       </c>
       <c r="B326" s="4">
         <v>43535</v>
       </c>
-      <c r="C326" s="6">
+      <c r="C326" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D326" s="6">
         <v>490440</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4">
       <c r="A327" s="1">
         <v>43497</v>
       </c>
       <c r="B327" s="4">
         <v>43556</v>
       </c>
-      <c r="C327" s="6">
+      <c r="C327" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D327" s="6">
         <v>491751</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4">
       <c r="A328" s="1">
         <v>43525</v>
       </c>
       <c r="B328" s="4">
         <v>43573</v>
       </c>
-      <c r="C328" s="6">
+      <c r="C328" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D328" s="6">
         <v>499292</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4">
       <c r="A329" s="1">
         <v>43556</v>
       </c>
       <c r="B329" s="4">
         <v>43600</v>
       </c>
-      <c r="C329" s="6">
+      <c r="C329" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D329" s="6">
         <v>499343</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4">
       <c r="A330" s="1">
         <v>43586</v>
       </c>
       <c r="B330" s="4">
         <v>43630</v>
       </c>
-      <c r="C330" s="6">
+      <c r="C330" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D330" s="6">
         <v>504741</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4">
       <c r="A331" s="1">
         <v>43617</v>
       </c>
       <c r="B331" s="4">
         <v>43662</v>
       </c>
-      <c r="C331" s="6">
+      <c r="C331" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D331" s="6">
         <v>505251</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4">
       <c r="A332" s="1">
         <v>43647</v>
       </c>
       <c r="B332" s="4">
         <v>43692</v>
       </c>
-      <c r="C332" s="6">
+      <c r="C332" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D332" s="6">
         <v>509091</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4">
       <c r="A333" s="1">
         <v>43678</v>
       </c>
       <c r="B333" s="4">
         <v>43721</v>
       </c>
-      <c r="C333" s="6">
+      <c r="C333" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D333" s="6">
         <v>512561</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4">
       <c r="A334" s="1">
         <v>43709</v>
       </c>
       <c r="B334" s="4">
         <v>43754</v>
       </c>
-      <c r="C334" s="6">
+      <c r="C334" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D334" s="6">
         <v>509282</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4">
       <c r="A335" s="1">
         <v>43739</v>
       </c>
       <c r="B335" s="4">
         <v>43784</v>
       </c>
-      <c r="C335" s="6">
+      <c r="C335" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D335" s="6">
         <v>510648</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4">
       <c r="A336" s="1">
         <v>43770</v>
       </c>
       <c r="B336" s="4">
         <v>43812</v>
       </c>
-      <c r="C336" s="6">
+      <c r="C336" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D336" s="6">
         <v>514215</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6">
       <c r="A337" s="1">
         <v>43800</v>
       </c>
       <c r="B337" s="4">
         <v>43846</v>
       </c>
-      <c r="C337" s="6">
+      <c r="C337" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D337" s="6">
         <v>515866</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6">
       <c r="A338" s="1">
         <v>43831</v>
       </c>
       <c r="B338" s="4">
         <v>43875</v>
       </c>
-      <c r="C338" s="6">
+      <c r="C338" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D338" s="6">
         <v>515119</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6">
       <c r="A339" s="1">
         <v>43862</v>
       </c>
       <c r="B339" s="4">
         <v>43907</v>
       </c>
-      <c r="C339" s="6">
+      <c r="C339" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D339" s="6">
         <v>515330</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6">
       <c r="A340" s="1">
         <v>43891</v>
       </c>
       <c r="B340" s="4">
         <v>43936</v>
       </c>
-      <c r="C340" s="6">
+      <c r="C340" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D340" s="6">
         <v>468324</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6">
       <c r="A341" s="1">
         <v>43922</v>
       </c>
       <c r="B341" s="4">
         <v>43966</v>
       </c>
-      <c r="C341" s="6">
+      <c r="C341" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D341" s="6">
         <v>401028</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6">
       <c r="A342" s="1">
         <v>43952</v>
       </c>
       <c r="B342" s="4">
         <v>43998</v>
       </c>
-      <c r="C342" s="6">
+      <c r="C342" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D342" s="6">
         <v>478449</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6">
       <c r="A343" s="1">
         <v>43983</v>
       </c>
       <c r="B343" s="4">
         <v>44028</v>
       </c>
-      <c r="C343" s="6">
+      <c r="C343" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D343" s="6">
         <v>518038</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6">
       <c r="A344" s="1">
         <v>44013</v>
       </c>
       <c r="B344" s="4">
         <v>44057</v>
       </c>
-      <c r="C344" s="6">
+      <c r="C344" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D344" s="6">
         <v>526304</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6">
       <c r="A345" s="1">
         <v>44044</v>
       </c>
       <c r="B345" s="4">
         <v>44090</v>
       </c>
-      <c r="C345" s="6">
+      <c r="C345" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D345" s="6">
         <v>530735</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6">
       <c r="A346" s="1">
         <v>44075</v>
       </c>
       <c r="B346" s="4">
         <v>44120</v>
       </c>
-      <c r="C346" s="6">
+      <c r="C346" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D346" s="6">
         <v>541302</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6">
       <c r="A347" s="1">
         <v>44105</v>
       </c>
       <c r="B347" s="4">
         <v>44152</v>
       </c>
-      <c r="C347" s="6">
+      <c r="C347" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D347" s="6">
         <v>539114</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6">
       <c r="A348" s="1">
         <v>44136</v>
       </c>
       <c r="B348" s="4">
         <v>44181</v>
       </c>
-      <c r="C348" s="6">
+      <c r="C348" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D348" s="6">
         <v>533941</v>
       </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E348" s="5">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="F348" s="5">
+        <v>5.4899999999999997E-2</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
       <c r="A349" s="1">
         <v>44166</v>
       </c>
       <c r="B349" s="4">
         <v>44211</v>
       </c>
-      <c r="C349" s="6">
+      <c r="C349" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D349" s="6">
         <v>538548</v>
       </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E349" s="5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F349" s="5">
+        <v>3.6799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
       <c r="A350" s="1">
         <v>44197</v>
       </c>
       <c r="B350" s="4">
         <v>44244</v>
       </c>
-      <c r="C350" s="6">
+      <c r="C350" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D350" s="6">
         <v>559230</v>
       </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E350" s="5">
+        <v>7.4300000000000005E-2</v>
+      </c>
+      <c r="F350" s="5">
+        <v>2.53E-2</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
       <c r="A351" s="1">
         <v>44228</v>
       </c>
       <c r="B351" s="4">
         <v>44271</v>
       </c>
-      <c r="C351" s="6">
+      <c r="C351" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D351" s="6">
         <v>544891</v>
       </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E351" s="5">
+        <v>6.2700000000000006E-2</v>
+      </c>
+      <c r="F351" s="5">
+        <v>9.5100000000000004E-2</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
       <c r="A352" s="1">
         <v>44256</v>
       </c>
       <c r="B352" s="4">
         <v>44301</v>
       </c>
-      <c r="C352" s="6">
+      <c r="C352" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D352" s="6">
         <v>603581</v>
       </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E352" s="5">
+        <v>0.28160000000000002</v>
+      </c>
+      <c r="F352" s="5">
+        <v>6.6600000000000006E-2</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
       <c r="A353" s="1">
         <v>44287</v>
       </c>
       <c r="B353" s="4">
         <v>44330</v>
       </c>
-      <c r="C353" s="6">
+      <c r="C353" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D353" s="6">
         <v>608961</v>
       </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E353" s="5">
+        <v>0.51219999999999999</v>
+      </c>
+      <c r="F353" s="5">
+        <v>0.29010000000000002</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
       <c r="A354" s="1">
         <v>44317</v>
       </c>
       <c r="B354" s="4">
         <v>44362</v>
       </c>
-      <c r="C354" s="6">
+      <c r="C354" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D354" s="6">
         <v>605282</v>
       </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E354" s="5">
+        <v>0.28149999999999997</v>
+      </c>
+      <c r="F354" s="5">
+        <v>0.53400000000000003</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
       <c r="A355" s="1">
         <v>44348</v>
       </c>
       <c r="B355" s="4">
         <v>44393</v>
       </c>
-      <c r="C355" s="6">
+      <c r="C355" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D355" s="6">
         <v>611950</v>
       </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E355" s="5">
+        <v>0.17979999999999999</v>
+      </c>
+      <c r="F355" s="5">
+        <v>0.27600000000000002</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
       <c r="A356" s="1">
         <v>44378</v>
       </c>
       <c r="B356" s="4">
         <v>44425</v>
       </c>
-      <c r="C356" s="6">
+      <c r="C356" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D356" s="6">
         <v>601817</v>
       </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E356" s="5">
+        <v>0.1578</v>
+      </c>
+      <c r="F356" s="5">
+        <v>0.18729999999999999</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
       <c r="A357" s="1">
         <v>44409</v>
       </c>
       <c r="B357" s="4">
         <v>44455</v>
       </c>
-      <c r="C357" s="6">
+      <c r="C357" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D357" s="6">
         <v>605533</v>
       </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E357" s="5">
+        <v>0.13450000000000001</v>
+      </c>
+      <c r="F357" s="5">
+        <v>0.15140000000000001</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
       <c r="A358" s="1">
         <v>44440</v>
       </c>
       <c r="B358" s="4">
         <v>44484</v>
       </c>
-      <c r="C358" s="6">
+      <c r="C358" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D358" s="6">
         <v>609671</v>
       </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E358" s="5">
+        <v>0.13950000000000001</v>
+      </c>
+      <c r="F358" s="5">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
       <c r="A359" s="1">
         <v>44470</v>
       </c>
       <c r="B359" s="4">
         <v>44516</v>
       </c>
-      <c r="C359" s="6">
+      <c r="C359" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D359" s="6">
         <v>618573</v>
       </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E359" s="5">
+        <v>0.16309999999999999</v>
+      </c>
+      <c r="F359" s="5">
+        <v>0.1426</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
       <c r="A360" s="1">
         <v>44501</v>
       </c>
       <c r="B360" s="4">
         <v>44545</v>
       </c>
-      <c r="C360" s="6">
+      <c r="C360" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D360" s="6">
         <v>624874</v>
       </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E360" s="5">
+        <v>0.18210000000000001</v>
+      </c>
+      <c r="F360" s="5">
+        <v>0.16259999999999999</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
       <c r="A361" s="1">
         <v>44531</v>
       </c>
       <c r="B361" s="4">
         <v>44575</v>
       </c>
-      <c r="C361" s="6">
+      <c r="C361" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D361" s="6">
         <v>619938</v>
       </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E361" s="5">
+        <v>0.16950000000000001</v>
+      </c>
+      <c r="F361" s="5">
+        <v>0.18240000000000001</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
       <c r="A362" s="1">
         <v>44562</v>
       </c>
       <c r="B362" s="4">
         <v>44608</v>
       </c>
-      <c r="C362" s="6">
+      <c r="C362" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D362" s="6">
         <v>631509</v>
       </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E362" s="5">
+        <v>0.12959999999999999</v>
+      </c>
+      <c r="F362" s="5">
+        <v>0.1671</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
       <c r="A363" s="1">
         <v>44593</v>
       </c>
       <c r="B363" s="4">
         <v>44636</v>
       </c>
-      <c r="C363" s="6">
+      <c r="C363" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D363" s="6">
         <v>638101</v>
       </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E363" s="5">
+        <v>0.1762</v>
+      </c>
+      <c r="F363" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
       <c r="A364" s="1">
         <v>44621</v>
       </c>
       <c r="B364" s="4">
         <v>44665</v>
       </c>
-      <c r="C364" s="6">
+      <c r="C364" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D364" s="6">
         <v>651027</v>
       </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E364" s="5">
+        <v>6.88E-2</v>
+      </c>
+      <c r="F364" s="5">
+        <v>0.18179999999999999</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
       <c r="A365" s="1">
         <v>44652</v>
       </c>
       <c r="B365" s="4">
         <v>44698</v>
       </c>
-      <c r="C365" s="6">
+      <c r="C365" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D365" s="6">
         <v>660194</v>
       </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E365" s="5">
+        <v>8.1900000000000001E-2</v>
+      </c>
+      <c r="F365" s="5">
+        <v>7.3400000000000007E-2</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
       <c r="A366" s="1">
         <v>44682</v>
       </c>
       <c r="B366" s="4">
         <v>44727</v>
       </c>
-      <c r="C366" s="6">
+      <c r="C366" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D366" s="6">
         <v>659847</v>
       </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E366" s="5">
+        <v>8.09E-2</v>
+      </c>
+      <c r="F366" s="5">
+        <v>7.8200000000000006E-2</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
       <c r="A367" s="1">
         <v>44713</v>
       </c>
       <c r="B367" s="4">
         <v>44757</v>
       </c>
-      <c r="C367" s="6">
+      <c r="C367" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D367" s="6">
         <v>666113</v>
       </c>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E367" s="5">
+        <v>8.4199999999999997E-2</v>
+      </c>
+      <c r="F367" s="5">
+        <v>8.1799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
       <c r="A368" s="1">
         <v>44743</v>
       </c>
       <c r="B368" s="4">
         <v>44790</v>
       </c>
-      <c r="C368" s="6">
+      <c r="C368" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D368" s="6">
         <v>659550</v>
       </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E368" s="5">
+        <v>0.1002</v>
+      </c>
+      <c r="F368" s="5">
+        <v>8.5400000000000004E-2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
       <c r="A369" s="1">
         <v>44774</v>
       </c>
       <c r="B369" s="4">
         <v>44819</v>
       </c>
-      <c r="C369" s="6">
+      <c r="C369" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D369" s="6">
         <v>663566</v>
       </c>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E369" s="5">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="F369" s="5">
+        <v>0.10059999999999999</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
       <c r="A370" s="1">
         <v>44805</v>
       </c>
       <c r="B370" s="4">
         <v>44848</v>
       </c>
-      <c r="C370" s="6">
+      <c r="C370" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D370" s="6">
         <v>661854</v>
       </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E370" s="5">
+        <v>8.4099999999999994E-2</v>
+      </c>
+      <c r="F370" s="5">
+        <v>9.4399999999999998E-2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
       <c r="A371" s="1">
         <v>44835</v>
       </c>
       <c r="B371" s="4">
         <v>44881</v>
       </c>
-      <c r="C371" s="6">
+      <c r="C371" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D371" s="6">
         <v>668671</v>
       </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E371" s="5">
+        <v>8.3699999999999997E-2</v>
+      </c>
+      <c r="F371" s="5">
+        <v>8.5900000000000004E-2</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
       <c r="A372" s="1">
         <v>44866</v>
       </c>
       <c r="B372" s="4">
         <v>44910</v>
       </c>
-      <c r="C372" s="6">
+      <c r="C372" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D372" s="6">
         <v>659458</v>
       </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E372" s="5">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="F372" s="5">
+        <v>7.51E-2</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
       <c r="A373" s="1">
         <v>44896</v>
       </c>
       <c r="B373" s="4">
         <v>44944</v>
       </c>
-      <c r="C373" s="6">
+      <c r="C373" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D373" s="6">
         <v>651763</v>
       </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E373" s="5">
+        <v>6.0199999999999997E-2</v>
+      </c>
+      <c r="F373" s="5">
+        <v>6.0100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
       <c r="A374" s="1">
         <v>44927</v>
       </c>
       <c r="B374" s="4">
         <v>44972</v>
       </c>
-      <c r="C374" s="6">
+      <c r="C374" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D374" s="6">
         <v>680253</v>
       </c>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E374" s="5">
+        <v>6.3799999999999996E-2</v>
+      </c>
+      <c r="F374" s="5">
+        <v>5.8900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
       <c r="A375" s="1">
         <v>44958</v>
       </c>
       <c r="B375" s="4">
         <v>45000</v>
       </c>
-      <c r="C375" s="6">
+      <c r="C375" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D375" s="6">
         <v>672152</v>
       </c>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E375" s="5">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="F375" s="5">
+        <v>7.6799999999999993E-2</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
       <c r="A376" s="1">
         <v>44986</v>
       </c>
       <c r="B376" s="4">
         <v>45030</v>
       </c>
-      <c r="C376" s="6">
+      <c r="C376" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D376" s="6">
         <v>665071</v>
       </c>
-    </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E376" s="5">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="F376" s="5">
+        <v>5.8799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
       <c r="A377" s="1">
         <v>45017</v>
       </c>
       <c r="B377" s="4">
         <v>45062</v>
       </c>
-      <c r="C377" s="6">
+      <c r="C377" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D377" s="6">
         <v>670494</v>
       </c>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E377" s="5">
+        <v>1.6E-2</v>
+      </c>
+      <c r="F377" s="5">
+        <v>2.4199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
       <c r="A378" s="1">
         <v>45047</v>
       </c>
       <c r="B378" s="4">
         <v>45092</v>
       </c>
-      <c r="C378" s="6">
+      <c r="C378" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D378" s="6">
         <v>673902</v>
       </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E378" s="5">
+        <v>1.61E-2</v>
+      </c>
+      <c r="F378" s="5">
+        <v>1.23E-2</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
       <c r="A379" s="1">
         <v>45078</v>
       </c>
       <c r="B379" s="4">
         <v>45125</v>
       </c>
-      <c r="C379" s="6">
+      <c r="C379" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D379" s="6">
         <v>677117</v>
       </c>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E379" s="5">
+        <v>1.49E-2</v>
+      </c>
+      <c r="F379" s="5">
+        <v>1.9599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
       <c r="A380" s="1">
         <v>45108</v>
       </c>
       <c r="B380" s="4">
         <v>45153</v>
       </c>
-      <c r="C380" s="6">
+      <c r="C380" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D380" s="6">
         <v>678424</v>
       </c>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E380" s="5">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="F380" s="5">
+        <v>1.5900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
       <c r="A381" s="1">
         <v>45139</v>
       </c>
       <c r="B381" s="4">
         <v>45183</v>
       </c>
-      <c r="C381" s="6">
+      <c r="C381" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D381" s="6">
         <v>684755</v>
       </c>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E381" s="5">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="F381" s="5">
+        <v>2.64E-2</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
       <c r="A382" s="1">
         <v>45170</v>
       </c>
       <c r="B382" s="4">
         <v>45216</v>
       </c>
-      <c r="C382" s="6">
+      <c r="C382" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D382" s="6">
         <v>689403</v>
       </c>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E382" s="5">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F382" s="5">
+        <v>2.8899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
       <c r="A383" s="1">
         <v>45200</v>
       </c>
       <c r="B383" s="4">
         <v>45245</v>
       </c>
-      <c r="C383" s="6">
+      <c r="C383" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D383" s="6">
         <v>686148</v>
       </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E383" s="5">
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="F383" s="5">
+        <v>4.0500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
       <c r="A384" s="1">
         <v>45231</v>
       </c>
       <c r="B384" s="4">
         <v>45274</v>
       </c>
-      <c r="C384" s="6">
+      <c r="C384" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D384" s="6">
         <v>685328</v>
       </c>
-    </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E384" s="5">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="F384" s="5">
+        <v>2.24E-2</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
       <c r="A385" s="1">
         <v>45261</v>
       </c>
       <c r="B385" s="4">
         <v>45308</v>
       </c>
-      <c r="C385" s="6">
+      <c r="C385" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D385" s="6">
         <v>686277</v>
       </c>
-    </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E385" s="5">
+        <v>5.5899999999999998E-2</v>
+      </c>
+      <c r="F385" s="5">
+        <v>3.9699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6">
       <c r="A386" s="1">
         <v>45292</v>
       </c>
       <c r="B386" s="4">
         <v>45337</v>
       </c>
-      <c r="C386" s="6">
+      <c r="C386" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D386" s="6">
         <v>680456</v>
       </c>
-    </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E386" s="5">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="F386" s="5">
+        <v>5.3100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6">
       <c r="A387" s="1">
         <v>45323</v>
       </c>
       <c r="B387" s="4">
         <v>45365</v>
       </c>
-      <c r="C387" s="6">
+      <c r="C387" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D387" s="6">
         <v>685280</v>
       </c>
-    </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E387" s="5">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F387" s="5">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6">
       <c r="A388" s="1">
         <v>45352</v>
       </c>
       <c r="B388" s="4">
         <v>45397</v>
       </c>
-      <c r="C388" s="6">
+      <c r="C388" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D388" s="6">
         <v>687641</v>
       </c>
-    </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E388" s="5">
+        <v>4.02E-2</v>
+      </c>
+      <c r="F388" s="5">
+        <v>2.1100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6">
       <c r="A389" s="1">
         <v>45383</v>
       </c>
       <c r="B389" s="4">
         <v>45427</v>
       </c>
-      <c r="C389" s="6">
+      <c r="C389" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D389" s="6">
         <v>687602</v>
       </c>
-    </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E389" s="5">
+        <v>3.04E-2</v>
+      </c>
+      <c r="F389" s="5">
+        <v>3.8300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6">
       <c r="A390" s="1">
         <v>45413</v>
       </c>
       <c r="B390" s="4">
         <v>45461</v>
       </c>
-      <c r="C390" s="6">
+      <c r="C390" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D390" s="6">
         <v>692774</v>
       </c>
-    </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E390" s="5">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="F390" s="5">
+        <v>2.7400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6">
       <c r="A391" s="1">
         <v>45444</v>
       </c>
       <c r="B391" s="4">
         <v>45489</v>
       </c>
-      <c r="C391" s="6">
+      <c r="C391" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D391" s="6">
         <v>692449</v>
       </c>
-    </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E391" s="5">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="F391" s="5">
+        <v>2.5899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6">
       <c r="A392" s="1">
         <v>45474</v>
       </c>
       <c r="B392" s="4">
         <v>45519</v>
       </c>
-      <c r="C392" s="6">
+      <c r="C392" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D392" s="6">
         <v>698835</v>
       </c>
-    </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E392" s="5">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="F392" s="5">
+        <v>2.0400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6">
       <c r="A393" s="1">
         <v>45505</v>
       </c>
       <c r="B393" s="4">
         <v>45552</v>
       </c>
-      <c r="C393" s="6">
+      <c r="C393" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D393" s="6">
         <v>697039</v>
       </c>
-    </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E393" s="5">
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="F393" s="5">
+        <v>2.86E-2</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6">
       <c r="A394" s="1">
         <v>45536</v>
       </c>
       <c r="B394" s="4">
         <v>45582</v>
       </c>
-      <c r="C394" s="6">
+      <c r="C394" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D394" s="6">
         <v>703285</v>
       </c>
-    </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E394" s="5">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="F394" s="5">
+        <v>2.1600000000000001E-2</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6">
       <c r="A395" s="1">
         <v>45566</v>
       </c>
       <c r="B395" s="4">
         <v>45611</v>
       </c>
-      <c r="C395" s="6">
+      <c r="C395" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D395" s="6">
         <v>707613</v>
       </c>
-    </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E395" s="5">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="F395" s="5">
+        <v>1.9800000000000002E-2</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6">
       <c r="A396" s="1">
         <v>45597</v>
       </c>
       <c r="B396" s="4">
         <v>45643</v>
       </c>
-      <c r="C396" s="6">
+      <c r="C396" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D396" s="6">
         <v>712145</v>
       </c>
-      <c r="D396" s="5">
+      <c r="E396" s="5">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="E396" s="5">
+      <c r="F396" s="5">
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6">
       <c r="A397" s="1">
         <v>45627</v>
       </c>
       <c r="B397" s="4">
         <v>45673</v>
       </c>
-      <c r="C397" s="6">
+      <c r="C397" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D397" s="6">
         <v>717662</v>
       </c>
-      <c r="D397" s="5">
+      <c r="E397" s="5">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="E397" s="5">
+      <c r="F397" s="5">
         <v>4.1200000000000001E-2</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6">
       <c r="A398" s="1">
         <v>45658</v>
       </c>
       <c r="B398" s="4">
         <v>45702</v>
       </c>
-      <c r="C398" s="6">
+      <c r="C398" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D398" s="6">
         <v>711461</v>
       </c>
-      <c r="D398" s="5">
+      <c r="E398" s="5">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="E398" s="5">
+      <c r="F398" s="5">
         <v>4.36E-2</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6">
       <c r="A399" s="1">
         <v>45689</v>
       </c>
       <c r="B399" s="4">
         <v>45733</v>
       </c>
-      <c r="C399" s="6">
+      <c r="C399" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D399" s="6">
         <v>711757</v>
       </c>
-      <c r="D399" s="5">
+      <c r="E399" s="5">
         <v>3.1E-2</v>
       </c>
-      <c r="E399" s="5">
+      <c r="F399" s="5">
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6">
       <c r="A400" s="1">
         <v>45717</v>
       </c>
       <c r="B400" s="4">
         <v>45763</v>
       </c>
-      <c r="C400" s="6">
+      <c r="C400" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D400" s="6">
         <v>722572</v>
       </c>
-      <c r="D400" s="5">
+      <c r="E400" s="5">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="E400" s="5">
+      <c r="F400" s="5">
         <v>3.5400000000000001E-2</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6">
       <c r="A401" s="1">
         <v>45748</v>
       </c>
       <c r="B401" s="4">
         <v>45792</v>
       </c>
-      <c r="C401" s="6">
+      <c r="C401" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D401" s="6">
         <v>721789</v>
       </c>
-      <c r="D401" s="5">
+      <c r="E401" s="5">
         <v>5.16E-2</v>
       </c>
-      <c r="E401" s="5">
+      <c r="F401" s="5">
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6">
       <c r="A402" s="1">
         <v>45778</v>
       </c>
       <c r="B402" s="4">
         <v>45825</v>
       </c>
-      <c r="C402" s="6">
+      <c r="C402" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D402" s="6">
         <v>716101</v>
       </c>
-      <c r="D402" s="5">
+      <c r="E402" s="5">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="E402" s="5">
+      <c r="F402" s="5">
         <v>0.05</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6">
       <c r="A403" s="1">
         <v>45809</v>
       </c>
       <c r="B403" s="4">
         <v>45855</v>
       </c>
-      <c r="C403" s="6">
+      <c r="C403" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D403" s="6">
         <v>723033</v>
       </c>
-      <c r="D403" s="5">
+      <c r="E403" s="5">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="E403" s="5">
+      <c r="F403" s="5">
         <v>3.2899999999999999E-2</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6">
       <c r="A404" s="1">
         <v>45839</v>
       </c>
       <c r="B404" s="4">
         <v>45884</v>
       </c>
-      <c r="C404" s="6">
+      <c r="C404" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D404" s="6">
         <v>727727</v>
       </c>
-      <c r="D404" s="5">
+      <c r="E404" s="5">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="E404" s="5">
+      <c r="F404" s="5">
         <v>4.3499999999999997E-2</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6">
       <c r="A405" s="1">
         <v>45870</v>
       </c>
       <c r="B405" s="4">
         <v>45916</v>
       </c>
-      <c r="C405" s="6">
+      <c r="C405" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D405" s="6">
         <v>732059</v>
       </c>
-      <c r="D405" s="5">
+      <c r="E405" s="5">
         <v>0.05</v>
       </c>
-      <c r="E405" s="5">
+      <c r="F405" s="5">
         <v>4.0899999999999999E-2</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6">
       <c r="A406" s="1">
         <v>45901</v>
       </c>
       <c r="B406" s="4">
         <v>45986</v>
       </c>
-      <c r="C406" s="6">
+      <c r="C406" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D406" s="6">
         <v>733258</v>
       </c>
-      <c r="D406" s="5">
+      <c r="E406" s="5">
         <v>4.2599999999999999E-2</v>
       </c>
-      <c r="E406" s="5">
+      <c r="F406" s="5">
         <v>5.0200000000000002E-2</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6">
       <c r="A407" s="1">
         <v>45931</v>
       </c>
       <c r="B407" s="4">
         <v>46007</v>
       </c>
-      <c r="C407" s="6">
+      <c r="C407" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D407" s="6">
         <v>732633</v>
       </c>
-      <c r="D407" s="5">
+      <c r="E407" s="5">
         <v>3.4700000000000002E-2</v>
       </c>
-      <c r="E407" s="5">
+      <c r="F407" s="5">
         <v>4.1799999999999997E-2</v>
       </c>
     </row>
@@ -5042,9 +6568,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D57F73F-5FFC-47C2-9B16-318BC0BDC7A6}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3">
       <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
@@ -5052,7 +6578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3">
       <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
